--- a/test_results_all_101.xlsx
+++ b/test_results_all_101.xlsx
@@ -425,20 +425,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:N102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
-    <col width="100" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="77" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="5" max="5"/>
+    <col width="100" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
     <col width="77" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="77" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,45 +457,60 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Retrieval Top Score</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval Avg Top3 Score</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval Top Company</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>TinyLlama RAG</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>TinyLlama Time (s)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>TinyLlama Success</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Gemini RAG</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Gemini RAG Time (s)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Gemini RAG Success</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Gemini No RAG</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Gemini No RAG Time (s)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Gemini No RAG Success</t>
         </is>
@@ -508,33 +526,34 @@
 Role.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PPG Industries Inc.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>**Tier 1 Companies in General Automotive Role:**
 - PPG Industries Inc.
 - Linde + Wiemann
 - Stryten Energy
 - Robert Bosch LLC
-**Tier 1 Company with Tier 1/2 Classification and EV Supply Chain Role (Tier 1 automotive components):**
-- Valeo</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+**Tier 1 Company with EV Battery Relevant Role:**
+- Valeo (EV Supply Chain Role: Tier 1 automotive components, EV / Battery Relevant: Yes)
+Note: No companies are categorized as both Tier 1 and Tier 2/3 in the provided context.</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.16</v>
+        <v>4.9</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -542,9 +561,20 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="N2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -558,7 +588,18 @@
 Product / Service, and Employment.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FREYR Battery</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>The company involved in Battery Pack activities is:
 - **Hyundai Motor Group**
@@ -568,32 +609,32 @@
   - **Employment:** 164</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
       <c r="G3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>0.11</v>
       </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
         <v>0.1</v>
       </c>
-      <c r="K3" t="b">
+      <c r="N3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -607,27 +648,27 @@
 linked to?</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Hitachi Astemo Americas Inc.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>The companies classified under Battery Cell in Georgia's EV supply chain are Hitachi Astemo Americas Inc., linked primarily to Hyundai Kia as the OEM.</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
       <c r="G4" t="n">
-        <v>0.11</v>
+        <v>1.06</v>
       </c>
       <c r="H4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -638,6 +679,17 @@
         <v>0.1</v>
       </c>
       <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -651,41 +703,52 @@
 Location and Primary Facility Type.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>The company involved in thermal management for the EV supply chain, along with its location and primary facility type, is:
-- **Company:** ZF Gainesville LLC
-  - **Location:** Georgia
-  - **Primary Facility Type:** Manufacturing (for Source 1) / Engineering / Operations (for Source 2)
-These sources indicate that ZF Gainesville LLC plays a significant role in EV thermal management and power electronics in the state of Georgia.</t>
-        </is>
+      <c r="C5" t="n">
+        <v>0.669</v>
       </c>
       <c r="D5" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
+        <v>0.652</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ZF Gainesville LLC</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>The company involved in thermal management for the EV supply chain in Georgia is:
+- **ZF Gainesville LLC**
+  - Location: Georgia
+  - Primary Facility Type: Manufacturing (for one entry) / Engineering / Operations (for another entry)
+This company plays a significant role in providing EV thermal management and power electronics, contributing to the state's EV supply chain capabilities.</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
         <v>0.1</v>
       </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="K5" t="b">
+      <c r="N5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -699,29 +762,33 @@
 provide?</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>The companies tagged as providing power electronics in Georgia's EV supply chain are Woory Industrial Co. and Yazaki North America. 
-- **Woory Industrial Co.** provides automotive connectors, terminals, sensors, and power/data components.
-- **Yazaki North America** offers automotive supplier division services including ADAS (Advanced Driver Assistance Systems), powertrain, and electronics.</t>
-        </is>
+      <c r="C6" t="n">
+        <v>0.54</v>
       </c>
       <c r="D6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="E6" t="b">
-        <v>1</v>
+        <v>0.522</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Woory Industrial Co.</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>The companies tagged as Power Electronics in Georgia's EV supply chain and their respective products/services are:
+1. **Woory Industrial Co.**
+   - **Product/Service:** Automotive connectors, terminals, sensors, and power/data components
+2. **Yazaki North America**
+   - **Product/Service:** Automotive supplier division (mobility solutions: ADAS, powertrain, electronics)
+3. **ZF Gainesville LLC**
+   - **Product/Service:** Automotive supplier footprint (electrification, thermal, powertrain, ADAS components)</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.14</v>
+        <v>2.39</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -729,9 +796,20 @@
         </is>
       </c>
       <c r="J6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
         <v>0.1</v>
       </c>
-      <c r="K6" t="b">
+      <c r="N6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -744,37 +822,52 @@
           <t>Show all Vehicle Assembly entities and summarize their Primary OEMs and Employment.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Based on the provided context about Georgia EV supply chain companies, there are no explicit vehicle assembly entities listed. All entries detail manufacturing plants or corporate operations related to automotive parts and components rather than full vehicle assembly. Therefore, no summary of Vehicle Assembly entities, their Primary OEMs, and Employment can be provided from this information.</t>
-        </is>
+      <c r="C7" t="n">
+        <v>0.637</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E7" t="b">
-        <v>1</v>
+        <v>0.631</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Vernay</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>Based on the provided context about Georgia EV supply chain companies, there are no explicit vehicle assembly entities listed. The companies mentioned are primarily involved in manufacturing parts and components rather than assembling vehicles. However, if we consider those with significant employment numbers as potentially key players in a broader assembly or major component production role:
+1. **Vernay** - Employment: 1600 | Primary OEMs: Hyundai/Kia
+2. **Toyota Industries Group (TACG-TICA)** - Employment: 18,100 | Primary OEMs: Freightliner/Western Star
+3. **TN Americas Holding Inc.** - Employment: 19,600 | Primary OEMs: Volvo/Mack, buses, construction equipment
+These companies have substantial employment numbers and are linked to major OEMs, indicating they play significant roles in the supply chain that could include assembly or large-scale component manufacturing for electric vehicles.</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
         <v>0.1</v>
       </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0.09</v>
-      </c>
       <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -788,14 +881,25 @@
 Role and Category.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Here are the companies in Georgia that have "EV / Battery Relevant" set to Yes along with their EV Supply Chain Role and Category:
+      <c r="C8" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Hitachi Astemo Americas Inc.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Here are the companies in Georgia with "EV / Battery Relevant" set to Yes along with their EV Supply Chain Role and Category:
 1. **Hitachi Astemo Americas Inc.**
    - EV Supply Chain Role: Battery Cell
    - Category: Tier 1/2
-2. **ZF Gainesville LLC** (Multiple entries, consolidated roles)
-   - EV Supply Chain Role: EV thermal management and power electronics, EV body, powertrain, and thermal components, EV thermal systems and electronics
+2. **ZF Gainesville LLC** (Multiple Entries)
+   - EV Supply Chain Role: EV thermal management and power electronics, EV thermal systems and electronics, EV body, powertrain, and thermal components
    - Category: OEM Supply Chain
 3. **Woodbridge Foam Corp.**
    - EV Supply Chain Role: EV wiring harnesses and power distribution
@@ -811,32 +915,32 @@
    - Category: OEM Footprint</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
       <c r="G8" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
         <v>0.1</v>
       </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K8" t="b">
+      <c r="N8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -850,7 +954,18 @@
 Yes? Provide the roles and the matching companies.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Woodbridge Foam Corp.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>The EV Supply Chain Roles that have at least one company with "EV / Battery Relevant = Yes" are:
 1. **EV wiring harnesses and power distribution** - Woodbridge Foam Corp.
@@ -860,22 +975,11 @@
 5. **High-voltage EV connectors and electronics** - Woory Industrial Co.</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="E9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
       <c r="G9" t="n">
-        <v>0.12</v>
+        <v>2.41</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -886,6 +990,17 @@
         <v>0.09</v>
       </c>
       <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -899,29 +1014,27 @@
 companies.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Among the battery pack and battery cell companies in Georgia, the Industry Group representation includes:
-- **Electronic and Other Electrical Equipment and Components**: Hitachi Astemo Americas Inc. (Battery Cells)
-There is no information provided about Battery Pack companies specifically within the given context. Therefore, only one Industry Group can be identified based on the available data.</t>
-        </is>
+      <c r="C10" t="n">
+        <v>0.616</v>
       </c>
       <c r="D10" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="E10" t="b">
-        <v>1</v>
+        <v>0.61</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Hitachi Astemo Americas Inc.</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>The Industry Group "Electronic and Other Electrical Equipment and Components" is represented among Battery Cell companies in Georgia EV supply chain. This can be seen with Hitachi Astemo Americas Inc., which manufactures battery cells for electric mobility. No other companies listed specifically fall under the category of Battery Pack, so this is the only relevant industry group provided based on the context given.</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.11</v>
+        <v>1.85</v>
       </c>
       <c r="H10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -932,6 +1045,17 @@
         <v>0.09</v>
       </c>
       <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -945,34 +1069,34 @@
 OEM Footprint), count how many companies are in the dataset.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Valeo</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Based on the provided context:
-- **Tier 1**: 0 companies listed.
-- **Tier 1/2**: 0 companies listed.
-- **Tier 2/3**: 0 companies listed.
+- **Tier 1**: 0 companies listed under this category.
+- **Tier 2/3**: 0 companies listed under this category.
+- **Tier 1/2**: 0 companies listed under this category.
+- **OEM (Footprint)**: 3 companies (Toyota Industries Group (TACG-TICA), Trenton Pressing, TN Americas Holding Inc.).
 - **OEM Supply Chain**: 4 companies (Valeo, Vista Metals Corp., Wabash National Corp., Volvo Group North America).
-- **OEM (Footprint)**: 3 companies (Toyota Industries Group (TACG-TICA), Trenton Pressing, TN Americas Holding Inc.).
-- **OEM Footprint**: Not explicitly listed as a separate category but can be considered under "OEM (Footprint)".
-The dataset includes companies categorized under OEM Supply Chain and OEM (Footprint) only.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+- **OEM Footprint** (Note: This is a duplicate of OEM (Footprint) in the context): 3 companies (Toyota Industries Group (TACG-TICA), Trenton Pressing, TN Americas Holding Inc.).
+The dataset does not include any companies under Tier 1 or Tier 2/3 categories.</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.13</v>
+        <v>3.78</v>
       </c>
       <c r="H11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -980,9 +1104,20 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -996,9 +1131,20 @@
 Role, and Employment.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Here are the companies located in Troup County along with their Category, EV Supply Chain Role, and Employment:
+      <c r="C12" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PPG Industries Inc.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Here are the companies located in Troup County along with their category, EV supply chain role, and employment:
 1. **PPG Industries Inc.**
    - Category: Tier 1
    - EV Supply Chain Role: General Automotive
@@ -1021,32 +1167,32 @@
    - Employment: 266</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="G12" t="n">
         <v>4.04</v>
       </c>
-      <c r="E12" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
         <v>0.1</v>
       </c>
-      <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>0.09</v>
-      </c>
       <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1060,31 +1206,32 @@
 the top 5 counties.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Haering Precision USA LP</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Based on the provided context, only one company is categorized as a Tier 1 supplier:
 - **Linde + Wiemann** in Troup County
-Since there are no other Tier 1 suppliers listed from Georgia, Troup County has the highest number of Tier 1 suppliers with just one. There are not enough data points to determine a top 5 list for counties with the most Tier 1 suppliers.
-Therefore:
-- **Troup County**: 1 Tier 1 supplier</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="E13" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+Since there are no other Tier 1 suppliers listed from other counties, Troup County has the highest number of Tier 1 suppliers with 1. Therefore, the top 5 counties by the count of Tier 1 suppliers would simply be:
+1. Troup County: 1
+2. No other county is listed with a Tier 1 supplier.
+Thus, only Troup County meets the criteria for having any Tier 1 suppliers in Georgia's EV supply chain context provided here.</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.1</v>
+        <v>2.74</v>
       </c>
       <c r="H13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1095,6 +1242,17 @@
         <v>0.09</v>
       </c>
       <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N13" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1108,7 +1266,18 @@
 Product / Service.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Grudem</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>The companies located in Gwinnett County along with their Industry Groups and Product/Services are:
 1. **Grudem**
@@ -1119,31 +1288,20 @@
    - Product/Service: Rubber powders for tires
 3. **Morgan Corp.**
    - Industry Group: Transportation Equipment
-   - Product/Service: Engine components, turbochargers, exhaust parts and other automotive parts (Charging Infrastructure role)
+   - Product/Service: Engine components, turbochargers, exhaust parts and other automotive parts
 4. **Michelin Tread Technologies**
-   - Industry Group: Not specified in the provided context
+   - Industry Group: Not specified (Automotive accessories)
    - Product/Service: Ventvisors, hood shields, floor mats, automotive accessories
 5. **MAT Heavy Duty**
-   - Industry Group: Not specified in the provided context
+   - Industry Group: Not specified (Vehicle protection and interior comfort products)
    - Product/Service: Vehicle protection and interior comfort products</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="E14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
       <c r="G14" t="n">
-        <v>0.12</v>
+        <v>3.79</v>
       </c>
       <c r="H14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1154,6 +1312,17 @@
         <v>0.09</v>
       </c>
       <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N14" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1167,27 +1336,27 @@
 Relevant status.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>FREYR Battery</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>There are no companies listed in the provided context that are located in Hall County. Therefore, no information can be provided regarding companies in Hall County based on the given data.</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E15" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
       <c r="G15" t="n">
-        <v>0.1</v>
+        <v>1.21</v>
       </c>
       <c r="H15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1195,9 +1364,20 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1211,40 +1391,56 @@
 the matching companies.</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Valeo</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>The city that has both Tier 1 and Tier 2/3 companies present is Troup County. 
 - **Tier 1 Company:** Linde + Wiemann (6-speed automatic transmissions)
 - **Tier 2/3 Companies:** No other Tier 2/3 company listed in Troup County, but it hosts the only Tier 1 company mentioned.
-However, if we consider broader definitions or potential oversight in the provided data, no city strictly fits both criteria with clear entries for both tiers. The closest match is Troup County with a Tier 1 presence and an implied need for Tier 2/3 suppliers to support its operations indirectly.</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="E16" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+However, if we consider cities with multiple companies regardless of their tier classification strictly from the given data:
+**Statesboro, Bulloch County:**
+- Tier 2/3 Company: Ascend Elements (Interior and exterior plastic parts)
+**Albany, Dougherty County:**
+- Tier 2/3 Companies: First American Resources (Honeycomb material) 
+Since Statesboro and Albany have multiple companies but only one is Tier 2/3 with no Tier 1 company listed in the context provided, Troup County remains the sole location meeting the criteria of having both tiers if we strictly adhere to the question's requirement.</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
         <v>0.1</v>
       </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>0.09</v>
-      </c>
       <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1258,28 +1454,28 @@
 companies in each county.</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>The only company listed as having an EV Supply Chain Role of "Battery Pack" is Hyundai Motor Group, located in McDonough, Henry County. Therefore:
+      <c r="C17" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>FREYR Battery</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>The only company involved in Battery Pack production mentioned in the context is Hyundai Motor Group, located in McDonough, Henry County. Therefore:
 - **Henry County**: Hyundai Motor Group</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
       <c r="G17" t="n">
-        <v>0.1</v>
+        <v>1.11</v>
       </c>
       <c r="H17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1287,9 +1483,20 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1303,37 +1510,48 @@
 and the summed Employment.</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>The county with the highest total employment across all companies is Cherokee County, with a summed employment of 1010 (JTEKT North America Corp. with 860 employees and Blue Ridge Manufacturing with 150 employees).</t>
-        </is>
+      <c r="C18" t="n">
+        <v>0.405</v>
       </c>
       <c r="D18" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Maxxis International USA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>The county with the highest total employment is Troup County, with a summed employment of 665 employees. This total includes Linde + Wiemann (515 employees) and ADVICS Manufacturing Georgia LLC (150 employees).</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
         <v>1.39</v>
       </c>
-      <c r="E18" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
         <v>0.1</v>
       </c>
-      <c r="H18" t="b">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>0.09</v>
-      </c>
       <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="N18" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1347,29 +1565,27 @@
 County.</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>The total employment by EV Supply Chain Role for companies located in Fulton County is as follows:
-- **General Automotive**: 400 (Elan Technology Inc. with 160 employees + SRG Global Inc. with 60 employees + Sewon America Inc. with 80 employees)
-Note: TI Fluid Systems has a North American Headquarters role influencing EV strategy but does not fall under the "General Automotive" supply chain role for employment calculation purposes based on the provided context.</t>
-        </is>
+      <c r="C19" t="n">
+        <v>0.606</v>
       </c>
       <c r="D19" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="E19" t="b">
-        <v>1</v>
+        <v>0.603</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Elan Technology Inc.</t>
+        </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>For companies located in Fulton County with an EV Supply Chain Role of "General Automotive," the total employment is 400. This includes Elan Technology Inc. (160 employees), SRG Global Inc. (60 employees), and Sewon America Inc. (80 employees). TI Fluid Systems has a different role ("OEM corporate footprint influencing EV strategy") and employs 19,600 people, which is not included in the total for "General Automotive" role.</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.13</v>
+        <v>2.36</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1377,9 +1593,20 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N19" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1393,9 +1620,20 @@
 summarize their Category and EV Supply Chain Role.</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>The companies with locations in Georgia are:
+      <c r="C20" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ADVICS Manufacturing Georgia LLC</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>The companies located in Georgia with their respective categories and EV supply chain roles are:
 1. **ADVICS Manufacturing Georgia LLC**
    - **Category:** Tier 2/3
    - **EV Supply Chain Role:** General Automotive
@@ -1416,22 +1654,11 @@
    - **EV Supply Chain Role:** OEM parent group footprint (EV + HD electrification)</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="E20" t="b">
-        <v>1</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
       <c r="G20" t="n">
-        <v>0.1</v>
+        <v>4.71</v>
       </c>
       <c r="H20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1439,9 +1666,20 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N20" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1454,41 +1692,51 @@
           <t>Show the distribution of companies by County for EV / Battery Relevant = Yes only.</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>The distribution of companies by county for those that are EV/Battery Relevant (Yes) is as follows:
+      <c r="C21" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>FREYR Battery</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>For companies with "EV / Battery Relevant" marked as "Yes," the distribution by county in Georgia is as follows:
 - **Bryan County**: Honda Development &amp; Manufacturing (400 employees)
 - **Hart County**: SK Battery America (75 employees)
-- **Coweta County**: Hitachi Astemo Americas Inc. (723 employees)
-- **Jackson County**: Thermal Ceramics Inc. (3000 employees)</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="E21" t="b">
-        <v>1</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+- **Coweta County**: Hitachi Astemo Americas Inc. (723 employees)</t>
         </is>
       </c>
       <c r="G21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
         <v>0.1</v>
       </c>
-      <c r="H21" t="b">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K21" t="b">
+      <c r="N21" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1501,27 +1749,27 @@
           <t>List all companies with Primary Facility Type = Headquarters (including North American</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Based on the provided context, there are no companies listed with a Primary Facility Type of "Headquarters" in Georgia's EV supply chain. All entries specify different types of facilities such as manufacturing plants or regional corporate operations but do not include any headquarters designation explicitly.</t>
-        </is>
+      <c r="C22" t="n">
+        <v>0.502</v>
       </c>
       <c r="D22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="E22" t="b">
-        <v>1</v>
+        <v>0.492</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>First American Resources</t>
+        </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>Based on the provided context about Georgia EV supply chain companies, there are no companies listed with a Primary Facility Type of "Headquarters" or "North American Headquarters." All entries specify different types of manufacturing plants or regional corporate operations. Therefore, no companies meet the criteria specified in the question.</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.1</v>
+        <v>1.61</v>
       </c>
       <c r="H22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1532,6 +1780,17 @@
         <v>0.1</v>
       </c>
       <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="N22" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1544,29 +1803,29 @@
           <t>Headquarters) and include their Location and Employment.</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Trenton Pressing</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>Based on the provided context about Georgia EV supply chain companies:
 - **Trenton Pressing** has its primary facility type as Regional corporate operations in Georgia with 350 employees.
-- **Toyota Industries Group (TACG-TICA)** operates a Corporate operations location in Georgia, employing 18,100 people.</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="E23" t="b">
-        <v>1</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+- **Toyota Industries Group (TACG-TICA)** operates a Corporate operations facility in Georgia, employing 18,100 people.</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.64</v>
+        <v>1.7</v>
       </c>
       <c r="H23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1574,9 +1833,20 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N23" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1590,37 +1860,48 @@
 they associated with?</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>None of the provided companies in the context have a Primary Facility Type listed as R&amp;D. The closest to research and development activities is ZF Gainesville LLC, which lists its Primary Facility Type as "Engineering / Operations," but this does not explicitly state R&amp;D. Therefore, there are no companies with Primary Facility Type = R&amp;D in the given information.</t>
-        </is>
+      <c r="C24" t="n">
+        <v>0.618</v>
       </c>
       <c r="D24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="E24" t="b">
-        <v>1</v>
+        <v>0.611</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ZF Gainesville LLC</t>
+        </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>None of the provided companies in the context have a Primary Facility Type listed as R&amp;D. The closest related to research and development activities is ZF Gainesville LLC, which has one entry with "Primary Facility Type: Engineering / Operations," but this does not match the specific type requested (R&amp;D).</t>
         </is>
       </c>
       <c r="G24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
         <v>0.1</v>
       </c>
-      <c r="H24" t="b">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="K24" t="b">
+      <c r="N24" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1634,7 +1915,18 @@
 Group.</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Toyota Industries Group (TACG-TICA)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>### Automotive Textiles and Interiors
 - **Wheelabrator Group Inc.**
@@ -1662,22 +1954,11 @@
   - Product / Service: Automotive metal stamping &amp; body parts manufacturing (Hyundai/Kia supplier)</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E25" t="b">
-        <v>1</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
       <c r="G25" t="n">
-        <v>1.72</v>
+        <v>4.79</v>
       </c>
       <c r="H25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1685,9 +1966,20 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N25" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1701,28 +1993,28 @@
 are EV / Battery Relevant = Yes?</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Among companies with Primary Facility Type containing 'Corporate operations' that are also EV/Battery Relevant = Yes, the relevant company is:
+      <c r="C26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Hitachi Astemo Americas Inc.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Among companies with Primary Facility Type containing 'Corporate operations' that are also EV/Battery Relevant = Yes, the company is:
 - TN Americas Holding Inc.</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E26" t="b">
-        <v>1</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
       <c r="G26" t="n">
-        <v>0.1</v>
+        <v>1.14</v>
       </c>
       <c r="H26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1730,9 +2022,20 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N26" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1746,27 +2049,27 @@
 Manufacturing, and list their Product / Service.</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Based on the provided context, there are no companies listed that have a Primary Facility Type containing both Engineering and Manufacturing. Therefore, I cannot provide any products or services for such companies as they do not exist in the given data set.</t>
-        </is>
+      <c r="C27" t="n">
+        <v>0.574</v>
       </c>
       <c r="D27" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E27" t="b">
-        <v>1</v>
+        <v>0.569</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ecoplastic Corporation</t>
+        </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>Based on the provided context, there are no companies listed that have a Primary Facility Type containing both Engineering and Manufacturing. All companies listed either have a facility type of "Manufacturing Plant" or "Regional corporate operations," but none combine Engineering with Manufacturing in their description. Therefore, there are no relevant Product / Service details to list for this criteria.</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.09</v>
+        <v>1.81</v>
       </c>
       <c r="H27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1774,9 +2077,20 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N27" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1789,7 +2103,18 @@
           <t>For each Primary Facility Type, compute the average Employment.</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Trenton Pressing</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>To calculate the average employment for each primary facility type based on the provided context:
 1. **Regional Corporate Operations**:
@@ -1806,26 +2131,15 @@
 3. **Manufacturing / OEM Operations**:
    - TI Fluid Systems (Employment: 80)
    Average Employment = \(80\) (only one company in this category)
-Summary of average employment by primary facility type:
-- Regional Corporate Operations</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>5.91</v>
-      </c>
-      <c r="E28" t="b">
-        <v>1</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+Summary of Averages:
+- Regional Corporate Operations: 12</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.1</v>
+        <v>5.89</v>
       </c>
       <c r="H28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1836,6 +2150,17 @@
         <v>0.09</v>
       </c>
       <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N28" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1848,29 +2173,29 @@
           <t>Which EV Supply Chain Role has the highest average Employment among Tier 1 suppliers?</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Woory Industrial Co.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>Based on the provided context, there is only one company listed as a Tier 1 supplier:
-- **PPG Industries Inc.** | Location: Troup County, Georgia | EV Supply Chain Role: General Automotive | Employment: 120
-Since PPG Industries Inc. is the sole Tier 1 supplier mentioned in the context and no other Tier 1 suppliers are listed, it cannot be determined that any specific EV Supply Chain Role has a higher average employment among Tier 1 suppliers based on this limited data. The answer can only reference PPG Industries Inc., which employs 120 people for its General Automotive role.</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="E29" t="b">
-        <v>1</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+- **PPG Industries Inc.** | Category: Tier 1 | Employment: 120
+Since this is the sole Tier 1 supplier mentioned in the sources and no other Tier 1 suppliers are listed, PPG Industries Inc. has the highest (and only) average employment among Tier 1 suppliers with 120 employees.</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.11</v>
+        <v>2.15</v>
       </c>
       <c r="H29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1878,9 +2203,20 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N29" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1894,37 +2230,48 @@
 Service.</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>There are no Tier 2/3 suppliers in the provided context that have employment of 500 or more. All listed Tier 2/3 suppliers have fewer than 500 employees.</t>
-        </is>
+      <c r="C30" t="n">
+        <v>0.534</v>
       </c>
       <c r="D30" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E30" t="b">
-        <v>1</v>
+        <v>0.525</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Adient</t>
+        </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>There are no Tier 2/3 suppliers listed in the provided context that have employment of 500 or more. All Tier 2/3 companies mentioned have fewer than 500 employees.</t>
         </is>
       </c>
       <c r="G30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H30" t="b">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
         <v>0.1</v>
       </c>
-      <c r="H30" t="b">
-        <v>0</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>0.09</v>
-      </c>
       <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="N30" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1937,30 +2284,30 @@
           <t>Find Tier 1/2 companies with EV / Battery Relevant = Yes and show their Primary OEMs.</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>The Tier 1/2 companies in Georgia with EV/Battery Relevant set to "Yes" and their corresponding primary Original Equipment Manufacturer (OEM) associations are:
+      <c r="C31" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Hitachi Astemo Americas Inc.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>The Tier 1/2 companies with EV/Battery Relevant set to "Yes" and their primary OEMs are:
 - **Hitachi Astemo Americas Inc.**
   - Primary OEMs: Hyundai Kia
-These companies play significant roles in the electric vehicle supply chain, focusing on battery cells and other critical components for EV manufacturing.</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="E31" t="b">
-        <v>1</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+These companies play significant roles in the electric vehicle supply chain according to the provided context.</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.11</v>
+        <v>1.64</v>
       </c>
       <c r="H31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1968,9 +2315,20 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N31" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1984,47 +2342,55 @@
 Provide counts and company lists.</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Among the listed Georgia EV supply chain companies:
-- **EV / Battery Relevant = Yes:** None of the provided sources list any materials companies as directly relevant to EV batteries.
-- **Indirect:** 
+      <c r="C32" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>TN Americas Holding Inc.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Among the provided Georgia EV supply chain companies:
+- **EV / Battery Relevant = Yes**: None of the listed materials companies have an "EV / Battery Relevant" status marked as Yes.
+- **Indirect**: 
   - Global Powertrain Systems LLC (Fabricates metal products, including coated coils, metal wall and roof systems and aluminum recreational vehicle doors)
   - FREYR Battery (Decorative and functional coating systems)
 Counts:
-- Directly Relevant: 0
-- Indirect: 2
-Company Lists:
-- Directly Relevant: None listed.
-- Indirect: Global Powertrain Systems LLC, FREYR Battery</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="E32" t="b">
-        <v>1</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+- EV / Battery Relevant = Yes: 0
+- Indirect: 2</t>
         </is>
       </c>
       <c r="G32" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="H32" t="b">
+        <v>1</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
         <v>0.1</v>
       </c>
-      <c r="H32" t="b">
-        <v>0</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>0.09</v>
-      </c>
       <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N32" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2038,38 +2404,38 @@
 top 3 Industry Groups by count?</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>The context provided lists five distinct Industry Groups for Georgia EV supply chain companies:
+      <c r="C33" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Toyota Industries Group (TACG-TICA)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>The context provided lists five distinct industry groups for Georgia EV supply chain companies:
 1. Commercial vehicles and powertrains (Toyota Industries Group)
 2. Automotive textiles and interiors (Wheelabrator Group Inc.)
 3. Automotive precision components (Trenton Pressing Inc.)
 4. Electrical connectors and sensors (Woory Industrial Co.)
 5. Automotive modules and components (Vista Metals Corp.)
-From the given context, only one company falls under each Industry Group, making it impossible to determine which has the largest number of companies based solely on this data. Therefore, no single Industry Group can be identified as having the largest count in this dataset.
+The largest industry group by count in the dataset is "Commercial vehicles and powertrains," with one company listed: Toyota Industries Group.
 The top 3 Industry Groups by count are:
-1. Commercial vehicles and powertrains (Toyota Industries Group)
-2. Automotive textiles and interiors (Wheelabrator Group Inc.)
-3. Automotive precision components (Trenton Pressing Inc.)
-Since each of these groups only has one company listed, they all share the same count.</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="E33" t="b">
-        <v>1</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+1. Commercial vehicles and powertrains
+2. Automotive textiles and interiors
+3. Automotive precision components
+Each of these groups has only one company listed in the provided context, making them tied for having the largest number within this limited dataset.</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.11</v>
+        <v>3.47</v>
       </c>
       <c r="H33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2077,9 +2443,20 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N33" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2093,30 +2470,30 @@
 the companies and their EV Supply Chain Role.</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Woory Industrial Co.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>Within the Industry Group 'Electrical connectors and sensors' (which falls under the broader category of Electronic and Other Electrical Equipment and Components), there is one company listed:
 - **Woory Industrial Co.**
   - EV Supply Chain Role: High-voltage EV connectors and electronics
-No other companies in Georgia fall strictly within the specified industry group based on the provided context.</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="E34" t="b">
-        <v>1</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+There are no companies explicitly listed in an industry group called 'Electronic and Other Electrical Equipment and Components' as per the provided context, but Woory Industrial Co. operates within a closely related field of electrical connectors and sensors.</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.1</v>
+        <v>2.26</v>
       </c>
       <c r="H34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2124,9 +2501,20 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N34" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2140,37 +2528,48 @@
 Relevant = Yes?</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Within the category of "Rubber and Miscellaneous Plastic Products," there is no company listed as EV/Battery Relevant = Yes. However, Woodbridge Foam Corp., which falls under the "Automotive electrical systems" Industry Group, is noted to be EV/Battery Relevant = Yes with its role in manufacturing EV wiring harnesses and power distribution systems.</t>
-        </is>
+      <c r="C35" t="n">
+        <v>0.5610000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="E35" t="b">
-        <v>1</v>
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>EVCO Plastics</t>
+        </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>Within the category of "Rubber and Miscellaneous Plastic Products," there is no company listed as EV/Battery Relevant = Yes. However, it's important to note that Woodbridge Foam Corp., which falls under the OEM Supply Chain rather than Rubber and Miscellaneous Plastic Products, is EV/Battery Relevant = Yes.</t>
         </is>
       </c>
       <c r="G35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H35" t="b">
+        <v>1</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
         <v>0.13</v>
       </c>
-      <c r="H35" t="b">
-        <v>0</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>0.09</v>
-      </c>
       <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N35" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2184,27 +2583,27 @@
 Relevant = Yes, and include Product / Service.</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Based on the provided context, there are no companies listed with an EV Supply Chain Role described as "General Automotive" where EV/Battery Relevant is set to Yes. All entries specify more detailed roles related to wiring harnesses, thermal management, power electronics, and other specific areas rather than a general automotive role in the electric vehicle supply chain. Therefore, no matches are found for the criteria specified in the question.</t>
-        </is>
+      <c r="C36" t="n">
+        <v>0.66</v>
       </c>
       <c r="D36" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Woodbridge Foam Corp.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Based on the provided context about Georgia EV supply chain companies, there are no companies listed with an EV Supply Chain Role described as "General Automotive" where EV/Battery Relevant is marked as Yes. The roles mentioned in the sources include specific functions such as wiring harnesses, thermal management, power electronics, and electrical architecture rather than a general automotive role. Therefore, no matches were found for the criteria specified in the question.</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
         <v>2.06</v>
       </c>
-      <c r="E36" t="b">
-        <v>1</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>0.1</v>
-      </c>
       <c r="H36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2215,6 +2614,17 @@
         <v>0.09</v>
       </c>
       <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="N36" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2228,27 +2638,27 @@
 Location?</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Based on the provided context, there are no companies listed that have a role specifically described as "Charging Infrastructure." The roles mentioned for the companies in Georgia include EV wiring harnesses and power distribution, high-voltage EV connectors and electronics, battery cells, OEM parent group footprint (EV + HD electrification), and electric truck strategy. Therefore, no relevant companies can be cited for the Charging Infrastructure role.</t>
-        </is>
+      <c r="C37" t="n">
+        <v>0.498</v>
       </c>
       <c r="D37" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="E37" t="b">
-        <v>1</v>
+        <v>0.495</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Woodbridge Foam Corp.</t>
+        </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>None of the provided companies are listed as being in the Charging Infrastructure role. The companies mentioned—Woodbridge Foam Corp., Woory Industrial Co., Hitachi Astemo Americas Inc., TN Americas Holding Inc., and Toyota Industries Group (TACG-TICA)—are involved in other roles within the EV supply chain such as wiring harnesses, connectors, battery cells, OEM footprints for electric vehicles, and commercial vehicle manufacturing.</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.1</v>
+        <v>2.04</v>
       </c>
       <c r="H37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2256,9 +2666,20 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K37" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N37" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2272,9 +2693,20 @@
 and Location.</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Here are the companies linked to Hyundai Kia with their respective details:
+      <c r="C38" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Hyundai Industrial Co.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Here are the companies linked to Hyundai Kia along with their category, EV supply chain role, and location:
 1. **Hyundai Industrial Co.**
    - **Category:** Tier 1/2
    - **EV Supply Chain Role:** General Automotive
@@ -2282,7 +2714,7 @@
 2. **Vernay**
    - **Category:** OEM Supply Chain
    - **EV Supply Chain Role:** Stamped and welded assemblies for OEMs
-   - **Location:** Georgia (specific county not provided)
+   - **Location:** Georgia (specific city not provided)
 3. **Hitachi Astemo Americas Inc.**
    - **Category:** Tier 1/2
    - **EV Supply Chain Role:** Battery Cell
@@ -2290,26 +2722,14 @@
 4. **Valeo**
    - **Category:** OEM Supply Chain
    - **EV Supply Chain Role:** Tier 1 automotive components
-   - **Location:** Georgia (specific county not provided)
-These companies are directly involved in the supply chain for Hyundai and Kia, providing various automotive parts and services.</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="E38" t="b">
-        <v>1</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+   - **Location:** Georgia (specific city not provided)</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.1</v>
+        <v>3.92</v>
       </c>
       <c r="H38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2320,6 +2740,17 @@
         <v>0.09</v>
       </c>
       <c r="K38" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2333,7 +2764,18 @@
 provide?</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.603</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Hyundai Industrial Co.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>The companies linked to Hyundai Motor Group and their respective products/services are:
 1. **Hyundai Industrial Co.**
@@ -2353,22 +2795,11 @@
    - Product/Service: Electric wiring components</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="G39" t="n">
         <v>3.86</v>
       </c>
-      <c r="E39" t="b">
-        <v>1</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>0.13</v>
-      </c>
       <c r="H39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2376,9 +2807,20 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="K39" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N39" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2391,7 +2833,18 @@
           <t>Identify suppliers linked to Rivian Automotive and show their Employment and Location.</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Rivian Automotive</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>The suppliers linked to Rivian Automotive are:
 1. **Rivian Automotive**  
@@ -2402,22 +2855,11 @@
    - Location: Calhoun, Gordon County</t>
         </is>
       </c>
-      <c r="D40" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="E40" t="b">
-        <v>1</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
       <c r="G40" t="n">
-        <v>0.1</v>
+        <v>1.66</v>
       </c>
       <c r="H40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2428,6 +2870,17 @@
         <v>0.09</v>
       </c>
       <c r="K40" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N40" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2441,29 +2894,29 @@
 Employment for those entries.</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>The only entry with "Primary OEMs: Multiple OEMs" is Adient. Since there is only one entry, the median employment for this category is 180. 
+      <c r="C41" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Valeo</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>The only entry with "Primary OEMs: Multiple OEMs" is Adient. Since there is only one entry, the median Employment value is 180. 
 Company: Adient  
 Employment: 180</t>
         </is>
       </c>
-      <c r="D41" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="E41" t="b">
-        <v>1</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
       <c r="G41" t="n">
-        <v>0.1</v>
+        <v>1.42</v>
       </c>
       <c r="H41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2471,9 +2924,20 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="K41" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N41" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2487,27 +2951,27 @@
 status do they have?</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Based on the provided context, there are no direct links specified between Mercedes-Benz USA LLC and any other company. However, Mercedes-Benz USA LLC is listed as having an "EV / Battery Relevant" status of "Indirect". This indicates that while it participates in the EV supply chain indirectly through its manufacturing activities, no specific supplier relationships with another company mentioned in the context are detailed regarding direct EV battery relevance.</t>
-        </is>
+      <c r="C42" t="n">
+        <v>0.903</v>
       </c>
       <c r="D42" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E42" t="b">
-        <v>1</v>
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz USA LLC</t>
+        </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>Based on the provided context, there are no direct links specified between Mercedes-Benz USA LLC and any other company. However, Mercedes-Benz USA LLC has an "EV / Battery Relevant" status of "Indirect," indicating it is involved in the EV supply chain but not directly related to battery manufacturing or cell production.</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.1</v>
+        <v>1.69</v>
       </c>
       <c r="H42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2518,6 +2982,17 @@
         <v>0.09</v>
       </c>
       <c r="K42" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N42" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2531,27 +3006,30 @@
 Chain Role and Location.</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>The company linked to SK Battery America based on the provided context is not directly associated with another specific company. However, SK Battery America itself plays an "Materials" role in the EV supply chain and is located in Hartwell, Hart County.</t>
-        </is>
+      <c r="C43" t="n">
+        <v>1.012</v>
       </c>
       <c r="D43" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E43" t="b">
-        <v>1</v>
+        <v>0.873</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>SK Battery America</t>
+        </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>The company linked to SK Battery America based on the provided context is not explicitly connected to another company through affiliation or supplier relationships. However, SK Battery America's own details are:
+- **EV Supply Chain Role:** Materials
+- **Location:** Hartwell, Hart County
+Since no other companies are directly cited as being affiliated with SK Battery America in the given sources, this information pertains solely to SK Battery America itself.</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="H43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2562,6 +3040,17 @@
         <v>0.1</v>
       </c>
       <c r="K43" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="N43" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2575,53 +3064,48 @@
 Product / Service.</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Based on the provided context, there are no companies explicitly linked to Club Car LLC. The listed companies in Georgia related to the EV supply chain are:
-1. **Woodbridge Foam Corp.**
-   - **EV Supply Chain Role:** EV wiring harnesses and power distribution
-   - **Product / Service:** Automotive wiring harnesses &amp; electrical distribution systems
-2. **Vista Metals Corp.**
-   - **EV Supply Chain Role:** EV and ICE component manufacturing
-   - **Product / Service:** Automotive modules/powertrain components; parts supply
-3. **ZF Gainesville LLC**
-   - **EV Supply Chain Role:** EV body, powertrain, and thermal components (Source 5)
-   - **Product / Service:** Contract manufacturing &amp; automotive systems (body, chassis, powertrain, e-drive)
-4. **ZF Gainesville LLC**
-   - **EV Supply Chain Role:** EV thermal management and power electronics (Sources 6 and 7)
-   - **Product / Service:** Automotive supplier footprint (electrification, thermal, powertrain, ADAS components)
-5. **Yamaha Motor Manufacturing Corp.**
-   - **EV Supply Chain Role:** Advanced electrical architecture for EVs
-   - **Product / Service:** Automotive electrical architecture, connectivity, and advanced safety components
-None of these companies are directly linked to Club Car LLC in the given context.</t>
-        </is>
+      <c r="C44" t="n">
+        <v>0.669</v>
       </c>
       <c r="D44" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="E44" t="b">
-        <v>1</v>
+        <v>0.662</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Woodbridge Foam Corp.</t>
+        </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>Based on the provided context, there are no direct links or associations mentioned between any of the listed companies (Woodbridge Foam Corp., Vista Metals Corp., ZF Gainesville LLC, Yamaha Motor Manufacturing Corp.) and Club Car LLC. Therefore, I cannot provide a list of companies linked to Club Car LLC with their EV Supply Chain Role and Product / Service as per your request.</t>
         </is>
       </c>
       <c r="G44" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H44" t="b">
+        <v>1</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K44" t="b">
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
         <v>0.1</v>
       </c>
-      <c r="H44" t="b">
-        <v>0</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K44" t="b">
+      <c r="N44" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2635,30 +3119,30 @@
 Facility Type?</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>The companies linked to Blue Bird or Blue Bird Corp. and their primary facility types are:
+      <c r="C45" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Blue Bird Corp.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>The companies linked to Blue Bird Corp. and their primary facility types are:
 1. **TE Connectivity** - Primary Facility Type: Manufacturing Plant (Located in Fort Valley, Peach County)
 2. **Hanon Systems USA LLC** - Primary Facility Type not specified (Located in Griffin, Spalding County)
 3. **Perkins Small Engines LLC** - Primary Facility Type not specified (Located in Zebulon, Pike County)</t>
         </is>
       </c>
-      <c r="D45" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="E45" t="b">
-        <v>1</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
       <c r="G45" t="n">
-        <v>0.1</v>
+        <v>2.05</v>
       </c>
       <c r="H45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2669,6 +3153,17 @@
         <v>0.1</v>
       </c>
       <c r="K45" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N45" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2682,9 +3177,20 @@
 Location, and Employment.</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Based on the provided context:
+      <c r="C46" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Yamaha Motor Manufacturing Corp.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Based on the provided context, the companies linked to Yamaha Motor Manufacturing Corp., including their category, location, and employment details are:
 1. **Teklas USA**
    - **Category:** OEM
    - **Location:** Coweta County, Georgia
@@ -2693,25 +3199,17 @@
    - **Category:** OEM Supply Chain
    - **Location:** Georgia
    - **Employment:** 298
-These companies are linked to Yamaha Motor Manufacturing Corp., either as a supplier or manufacturer in the EV supply chain.</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="E46" t="b">
-        <v>1</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+3. **Trenton Pressing (Footprint)**
+   - **Category:** OEM (Footprint)
+   - **Location:** Georgia
+   - **Employment:** 350</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.11</v>
+        <v>3.05</v>
       </c>
       <c r="H46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2719,9 +3217,20 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="K46" t="b">
+        <v>0</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N46" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2735,40 +3244,51 @@
 with it.</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Vista Metals Corp.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>Based on the provided context:
-- **TN Americas Holding Inc.**: 2 companies (listed twice in sources 2 and 7)
-- **Toyota Industries Group (TACG-TICA)**: 1 company
-Note: The question asks for Primary OEMs excluding blanks, which means we consider only those explicitly mentioned as parent groups or significant footprints in the EV supply chain context provided.</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="E47" t="b">
-        <v>1</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+- **TN Americas Holding Inc.**: 2 companies (Source 2 and Source 7)
+- **Toyota Industries Group (TACG-TICA)**: 1 company (Source 6)
+These are the only OEMs with associated companies listed in the given sources, excluding blanks or unspecified entries.</t>
         </is>
       </c>
       <c r="G47" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H47" t="b">
+        <v>1</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
         <v>0.1</v>
       </c>
-      <c r="H47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="J47" t="n">
-        <v>0.14</v>
-      </c>
       <c r="K47" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N47" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2782,27 +3302,27 @@
 (excluding blanks)?</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>TN Americas Holding Inc. has the highest total employment among the provided companies with 19,600 employees at its Georgia facility.</t>
-        </is>
+      <c r="C48" t="n">
+        <v>0.487</v>
       </c>
       <c r="D48" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E48" t="b">
-        <v>1</v>
+        <v>0.481</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>TN Americas Holding Inc.</t>
+        </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>The primary OEM with the highest total employment across its associated companies in Georgia is TN Americas Holding Inc., with 19,600 employees. This company is involved in commercial vehicles and powertrains and acts as an OEM parent group footprint for EV and HD electrification.</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.09</v>
+        <v>1.57</v>
       </c>
       <c r="H48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2813,6 +3333,17 @@
         <v>0.09</v>
       </c>
       <c r="K48" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N48" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2826,40 +3357,51 @@
 (e.g., entries like 'Hyundai Kia Rivian') and list them.</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Based on the provided context and focusing on the "Primary OEMs" field, the following companies supply to more than one OEM:
+      <c r="C49" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>NIFCO KTW America Corp.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Based on the provided context, the companies that supply to more than one OEM are:
 1. **NIFCO KTW America Corp.** - Primary OEMs: Multiple OEMs
 2. **Hyundai Industrial Co.** - Primary OEMs: Multiple OEMs
-These companies are listed as supplying to multiple Original Equipment Manufacturers (OEMs).</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="E49" t="b">
-        <v>1</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+These companies indicate they serve multiple Original Equipment Manufacturers (OEMs) in the automotive industry.</t>
         </is>
       </c>
       <c r="G49" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="H49" t="b">
+        <v>1</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K49" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
         <v>0.1</v>
       </c>
-      <c r="H49" t="b">
-        <v>0</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="K49" t="b">
+      <c r="N49" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2873,34 +3415,33 @@
 Product / Service.</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Among the companies listed in the context that are linked to Hyundai or Kia (and implicitly by extension to Rivian through supply chain connections), the following information is provided:
+      <c r="C50" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Vernay</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Based on the provided context, among the companies linked to Hyundai and Kia, the following are listed:
 1. **Vernay**
-   - EV Supply Chain Role: Stamped and welded assemblies for OEMs
-   - Product / Service: Automotive metal stamping &amp; body parts manufacturing
+   - **EV Supply Chain Role:** Stamped and welded assemblies for OEMs
+   - **Product / Service:** Automotive metal stamping &amp; body parts manufacturing (Hyundai/Kia supplier)
 2. **Valeo**
-   - EV Supply Chain Role: Tier 1 automotive components
-   - Product / Service: Automotive body/stamped metal assemblies
-These companies provide critical stamped and welded assemblies as well as tier 1 automotive components for OEMs, including Hyundai and Kia, which are relevant to the broader supply chain that may serve Rivian.</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="E50" t="b">
-        <v>1</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+   - **EV Supply Chain Role:** Tier 1 automotive components
+   - **Product / Service:** Automotive body/stamped metal assemblies (Kia/Hyundai supply chain)</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.11</v>
+        <v>2.4</v>
       </c>
       <c r="H50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2908,9 +3449,20 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="K50" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="N50" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2924,33 +3476,33 @@
 and Employment.</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>The companies linked to Porsche Cars North America Inc. in Georgia are:
+      <c r="C51" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Porsche Cars North America Inc.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>The companies linked to Porsche Cars North America Inc. are:
 1. **Minebea AccessSolutions USA Inc.**
-   - **Location:** Atlanta, Fulton County
-   - **Employment:** Not specified
-2. **Denkai America**
-   - **Location:** Cumming, Forsyth County
-   - **Employment:** 50</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="E51" t="b">
-        <v>1</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+   - Location: Atlanta, Fulton County
+   - Employment: Not specified
+2. **Porsche Cars North America Inc. (itself)**
+   - Location: Cairo, Grady County
+   - Employment: 125</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.1</v>
+        <v>1.84</v>
       </c>
       <c r="H51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2958,9 +3510,20 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="K51" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N51" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2974,31 +3537,31 @@
 Categories?</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Vista Metals Corp.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>The OEM-linked entries missing the "Supplier or Affiliation Type" field are:
 1. **Vista Metals Corp.** - Category: OEM Supply Chain
-2. **TN Americas Holding Inc.** (both instances) - Category: OEM (Footprint)
+2. **TN Americas Holding Inc. (listed twice but only one entry is OEM footprint)** - Category: OEM (Footprint)
 3. **Yamaha Motor Manufacturing Corp.** - Category: OEM Supply Chain
-These companies do not specify a "Supplier or Affiliation Type" in the provided context.</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="E52" t="b">
-        <v>1</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+These companies do not specify a Supplier or Affiliation Type in the provided context.</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.1</v>
+        <v>2.21</v>
       </c>
       <c r="H52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3009,6 +3572,17 @@
         <v>0.1</v>
       </c>
       <c r="K52" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N52" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3022,31 +3596,55 @@
 Locations?</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Based on the provided context about Georgia EV supply chain companies, the top 10 companies by employment along with their categories and locations are:
-1. Yazaki North America | Category: OEM Footprint | Location: Georgia | Employment: 230,000
-2. Toyota Industries Group (TACG-TICA) | Category: OEM (Footprint) | Location: Georgia | Employment: 18,100
-3. Woory Industrial Co. | Category: OEM Supply Chain | Location: Georgia | Employment: 87,000
-Note that the employment numbers for Trenton Pressing and Adient are significantly lower than the top three companies listed above (with 350 and 180 employees respectively), so they do not make it into the top 10. The provided context does not list enough companies to complete a full top 10, but these three have the highest employment figures given in the information.</t>
-        </is>
+      <c r="C53" t="n">
+        <v>0.423</v>
       </c>
       <c r="D53" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E53" t="b">
-        <v>1</v>
+        <v>0.416</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Toyota Industries Group (TACG-TICA)</t>
+        </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t xml:space="preserve">Based on the provided context, the top 10 companies by employment in Georgia's EV supply chain are:
+1. **Yazaki North America**
+   - Category: OEM Footprint
+   - Location: Georgia
+   - Employment: 230,000
+2. **Toyota Industries Group (TACG-TICA)**
+   - Category: OEM (Footprint)
+   - Location: Georgia
+   - Employment: 18,100
+3. **Woory Industrial Co.**
+   - Category: OEM Supply Chain
+   - Location: Georgia
+   - Employment: 87,000
+4. **Trenton Pressing**
+   - Category: OEM (Footprint)
+   - Location: Georgia
+   - Employment: 350
+Since the context only provides employment data for five companies with significant numbers and does not list others exceeding these figures, the remaining entries would be:
+5. **Adient**
+   - Category: Tier 2/3
+   - Location: Ringgold, Catoosa County
+   - Employment: 180
+6. **Trenton Pressing** (listed again for completeness as it's one of the companies with known employment)
+   - Category: OEM (Footprint)
+   - Location: Georgia
+   - Employment: 350
+7. **Wabash National Corp.**
+   - Category: OEM Supply Chain
+  </t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.1</v>
+        <v>5.88</v>
       </c>
       <c r="H53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3054,9 +3652,20 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="K53" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N53" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3070,42 +3679,55 @@
 Roles?</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>The two companies with the lowest employment numbers from the provided context are:
+      <c r="C54" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Woory Industrial Co.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>The two companies with the lowest employment numbers in Georgia's EV supply chain context are:
 1. **Vanguard National Trailer Corp.**
    - **EV Supply Chain Role:** Body and chassis components for EV and ICE OEMs
-2. **Woodbridge Foam Corp.** (listed twice but has the same employment number)
+2. **Woodbridge Foam Corp.** (listed twice but with slightly different details, both have similar employment figures)
    - **EV Supply Chain Role:** EV wiring harnesses and power distribution
-There are only two distinct companies with specific employment figures that fall into this category based on the provided context, both having significantly fewer employees than the others listed. Therefore, there aren't 10 companies meeting the criteria of lowest Employment as specified in your question.</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E54" t="b">
-        <v>1</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+Since only two companies are listed with distinct low employment numbers, the answer focuses on these:
+- Vanguard National Trailer Corp.: Body and chassis components for EV and ICE OEMs
+- Woodbridge Foam Corp.: EV wiring harnesses and power distribution</t>
         </is>
       </c>
       <c r="G54" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="H54" t="b">
+        <v>1</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
         <v>0.1</v>
       </c>
-      <c r="H54" t="b">
-        <v>0</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
-        <v>0.09</v>
-      </c>
       <c r="K54" t="b">
+        <v>0</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N54" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3119,27 +3741,27 @@
 Employment and what is its Product / Service?</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Woory Industrial Co.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>Among EV / Battery Relevant = Yes companies, Yazaki North America has the highest Employment with 230,000 employees. Its Product / Service includes automotive supplier division (mobility solutions: ADAS, powertrain, electronics).</t>
         </is>
       </c>
-      <c r="D55" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="E55" t="b">
-        <v>1</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
       <c r="G55" t="n">
-        <v>0.16</v>
+        <v>1.44</v>
       </c>
       <c r="H55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3150,6 +3772,17 @@
         <v>0.09</v>
       </c>
       <c r="K55" t="b">
+        <v>0</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N55" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3162,7 +3795,18 @@
           <t>Compare total Employment between EV / Battery Relevant groups (Yes vs Indirect vs No).</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>TN Americas Holding Inc.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>Among the provided Georgia EV supply chain companies:
 - **EV/Battery Relevant: Yes** includes TN Americas Holding Inc., TI Fluid Systems, Toyota Industries Group (TACG-TICA), Hitachi Astemo Americas Inc., and Yazaki North America. The total employment for these companies is:
@@ -3171,32 +3815,21 @@
   - Toyota Industries Group (TACG-TICA): 18100
   - Hitachi Astemo Americas Inc.: 723
   - Yazaki North America: 230000
-  Total employment for EV/Battery Relevant: Yes = **277423**
+  Total Employment for "Yes": **287423**
 - **EV/Battery Relevant: Indirect** includes Stryten Energy. The total employment is:
   - Stryten Energy: 50
-  Total employment for EV/Battery Relevant: Indirect = **50**
+  Total Employment for "Indirect": **50**
 - **EV/Battery Relevant: No** includes FREYR Battery. The total employment is:
   - FREYR Battery: 110
-  Total employment for EV/Battery Relevant: No = **110**
-In summary, the companies categorized as "Yes" have significantly higher total employment compared to those categorized as "Indirect" or "No."</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="E56" t="b">
-        <v>1</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+  Total Employment for "No": **110**
+In summary, the companies categorized as EV/Battery Relevant (Yes) have a significantly higher total employment compared to those classified as Indirect or No in relevance to EV batteries.</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.1</v>
+        <v>5.4</v>
       </c>
       <c r="H56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3204,9 +3837,20 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="K56" t="b">
+        <v>0</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N56" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3220,46 +3864,59 @@
 total Employment.</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>To determine the top 3 EV supply chain roles by total employment based on the provided context:
+      <c r="C57" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ZF Gainesville LLC</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Based on the provided context about Georgia EV supply chain companies:
 1. **EV thermal management and power electronics**: ZF Gainesville LLC (Employment: 17500)
-2. **Advanced electrical architecture for EVs**: Yamaha Motor Manufacturing Corp. (Employment: 190000)
-3. **Body, powertrain, and thermal components**: ZF Gainesville LLC (Employment: 170000)
-Note that the employment figures provided for ZF Gainesville LLC are inconsistent across sources (17500 vs. 170000). For this analysis, I've used the highest figure available as it likely represents the most comprehensive data point.
-The top three roles by total employment are:
-- Advanced electrical architecture for EVs: Yamaha Motor Manufacturing Corp. with 190000 employees.
-- Body, powertrain, and thermal components: ZF Gainesville LLC with 170000 employees.
-- EV thermal management and power electronics: ZF Gainesville LLC with 17500 employees.
-The total employment for these roles is calculated based on the highest figures provided.</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="E57" t="b">
-        <v>1</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+2. **EV body, powertrain, and thermal components**: ZF Gainesville LLC (Employment: 170000)
+3. **OEM parent group footprint (electric truck strategy)**: Toyota Industries Group (TACG-TICA) (Employment: 18100)
+4. **OEM parent group footprint (EV + HD electrification)**: TN Americas Holding Inc. (Employment: 19600)
+5. **EV wiring harnesses and power distribution**: Woodbridge Foam Corp. (Employment: 1657)
+6. **Advanced electrical architecture for EVs**: Yamaha Motor Manufacturing Corp. (Employment: 190000)
+7. **General Automotive**: Adient (Employment: 180) - Indirectly relevant
+8. **EV and ICE component manufacturing**: Vista Metals Corp. (Employment: 1500)
+The top three EV Supply Chain Roles by total Employment are:
+- **Advanced electrical architecture for EVs** (Yamaha Motor Manufacturing Corp.) with a total of 190,000 employees.
+- **EV body, powertrain, and thermal components** (ZF Gainesville LLC) with a total of 1</t>
         </is>
       </c>
       <c r="G57" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="H57" t="b">
+        <v>1</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K57" t="b">
+        <v>0</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
         <v>0.1</v>
       </c>
-      <c r="H57" t="b">
-        <v>0</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="K57" t="b">
+      <c r="N57" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3273,29 +3930,29 @@
 correspond to those extremes?</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Linde + Wiemann</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>For Tier 1 suppliers in Georgia's EV supply chain:
-- **Minimum Employment**: PPG Industries Inc. with 120 employees.
-- **Maximum Employment**: Linde + Wiemann with 515 employees.</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E58" t="b">
-        <v>1</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+- **Minimum Employment:** PPG Industries Inc. with 120 employees.
+- **Maximum Employment:** Linde + Wiemann with 515 employees.</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.11</v>
+        <v>1.39</v>
       </c>
       <c r="H58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3306,6 +3963,17 @@
         <v>0.09</v>
       </c>
       <c r="K58" t="b">
+        <v>0</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="N58" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3318,46 +3986,46 @@
           <t>Within Tier 2/3 suppliers, what is the average Employment by Industry Group?</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>To calculate the average employment for Tier 2/3 suppliers within each industry group based on the provided context:
+      <c r="C59" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Adient</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>To calculate the average employment for Tier 2/3 suppliers within each Industry Group based on the provided context:
 1. **Textile Products**:
-   - Adient: 180 employees
+   - Adient | Employment: 180
 2. **Rubber and Miscellaneous Plastic Products**:
-   - Bosch (Automotive Division): 250 employees
+   - Bosch (Automotive Division) | Employment: 250
 3. **Machinery Except Electrical**:
-   - Haering Precision USA LP: 200 employees
+   - Haering Precision USA LP | Employment: 200
 4. **Primary Metal Industries**:
-   - Ecoplastic Corporation: 160 employees
-   - Dongwon Autopart Technology Georgia LLC: 315 employees
-Average Employment by Industry Group for Tier 2/3 suppliers:
+   - Ecoplastic Corporation | Employment: 160
+   - Dongwon Autopart Technology Georgia LLC | Employment: 315
+Average employment for Tier 2/3 suppliers by Industry Group:
 - Textile Products: 180 (only one company)
 - Rubber and Miscellaneous Plastic Products: 250 (only one company)
 - Machinery Except Electrical: 200 (only one company)
-- Primary Metal Industries: \(\frac{160 + 315}{2} = 237.5\) employees
-Thus, the average employment by Industry Group for Tier 2/3 suppliers is:
+- Primary Metal Industries: (160 + 315) / 2 = 237.5
+Thus, the average employment for Tier 2/3 suppliers by Industry Group is as follows:
 - Textile Products: 180
 - Rubber and Miscellaneous Plastic Products: 250
 - Machinery Except Electrical: 200
 - Primary Metal Industries: 237.5</t>
         </is>
       </c>
-      <c r="D59" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="E59" t="b">
-        <v>1</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
       <c r="G59" t="n">
-        <v>0.12</v>
+        <v>5.52</v>
       </c>
       <c r="H59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3368,6 +4036,17 @@
         <v>0.09</v>
       </c>
       <c r="K59" t="b">
+        <v>0</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N59" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3380,27 +4059,27 @@
           <t>Which counties have the highest total Employment among Tier 1 suppliers only?</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>The county with the highest total employment among Tier 1 suppliers is Troup County. This is based on the data from Linde + Wiemann (515 employees) and PPG Industries Inc. (120 employees), which together total 635 employees in Troup County.</t>
-        </is>
+      <c r="C60" t="n">
+        <v>0.501</v>
       </c>
       <c r="D60" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="E60" t="b">
-        <v>1</v>
+        <v>0.496</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Linde + Wiemann</t>
+        </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>The county with the highest total employment among Tier 1 suppliers is Troup County. This is based on the data from Linde + Wiemann (515 employees) and PPG Industries Inc. (120 employees), totaling 635 employees in Troup County.</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.1</v>
+        <v>1.57</v>
       </c>
       <c r="H60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3408,9 +4087,20 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="K60" t="b">
+        <v>0</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N60" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3424,27 +4114,27 @@
 Chain Role?</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>MAT Heavy Duty</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>In Gwinnett County, Grudem has the highest employment with 807 employees. Its EV Supply Chain Role is General Automotive.</t>
         </is>
       </c>
-      <c r="D61" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E61" t="b">
-        <v>1</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
       <c r="G61" t="n">
-        <v>0.1</v>
+        <v>1.07</v>
       </c>
       <c r="H61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3455,6 +4145,17 @@
         <v>0.09</v>
       </c>
       <c r="K61" t="b">
+        <v>0</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N61" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3468,27 +4169,27 @@
 Employment and what is its Location?</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>None of the provided companies have a Primary Facility Type listed as R&amp;D. The companies listed have Primary Facility Types such as Regional corporate operations, Corporate operations, Manufacturing plant, and Engineering/Operations. Therefore, there is no company in this list that matches the criteria specified in the question.</t>
-        </is>
+      <c r="C62" t="n">
+        <v>0.432</v>
       </c>
       <c r="D62" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="E62" t="b">
-        <v>1</v>
+        <v>0.43</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Trenton Pressing</t>
+        </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>Based on the provided context, there are no companies listed with a Primary Facility Type of "R&amp;D". Therefore, it's not possible to identify any company meeting this criterion.</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.1</v>
+        <v>1.18</v>
       </c>
       <c r="H62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3496,9 +4197,20 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="K62" t="b">
+        <v>0</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N62" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3512,27 +4224,27 @@
 Relevant = Yes.</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Based on the provided context, there are no companies listed with employment between 200 and 500 employees (inclusive) that are EV/Battery Relevant = Yes.</t>
-        </is>
+      <c r="C63" t="n">
+        <v>0.573</v>
       </c>
       <c r="D63" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E63" t="b">
-        <v>1</v>
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Hitachi Astemo Americas Inc.</t>
+        </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>Based on the provided context, there is no company listed with employment between 200 and 500 employees (inclusive) that has "EV / Battery Relevant" marked as Yes. The closest in terms of employee numbers are Hitachi Astemo Americas Inc., which employs 723 people, but it falls outside the specified range.</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.09</v>
+        <v>1.82</v>
       </c>
       <c r="H63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3543,6 +4255,17 @@
         <v>0.09</v>
       </c>
       <c r="K63" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N63" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3555,27 +4278,27 @@
           <t>Which Industry Group has the highest total Employment across all companies?</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>The Industry Group with the highest total employment across all companies is **Electrical connectors and sensors**, with Woory Industrial Co. having 87,000 employees in Georgia.</t>
-        </is>
+      <c r="C64" t="n">
+        <v>0.432</v>
       </c>
       <c r="D64" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E64" t="b">
-        <v>1</v>
+        <v>0.43</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Toyota Industries Group (TACG-TICA)</t>
+        </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>The Industry Group with the highest total employment is **Electrical connectors and sensors**, with Woory Industrial Co. having 87,000 employees in Georgia.</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.1</v>
+        <v>1.15</v>
       </c>
       <c r="H64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3583,9 +4306,20 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="K64" t="b">
+        <v>0</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3599,54 +4333,53 @@
 highest average.</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Toyota Industries Group (TACG-TICA)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>To determine the category with the highest average employment based on the provided context:
-1. **OEM (Footprint)**:
-   - Toyota Industries Group (TACG-TICA): 18100 employees
-   - Trenton Pressing: 350 employees
-   - Average Employment = (18100 + 350) / 2 = 9225
-2. **Tier 2/3**:
-   - Adient: 180 employees
-   - Average Employment = 180
-3. **Tier 1**:
-   - Linde + Wiemann: 515 employees
-   - Average Employment = 515
-4. **OEM Supply Chain**:
-   - WIKA USA: 250,000 employees
-   - Valeo: 269 employees
-   - Volvo Cars USA: 456 employees
-   - Wabash National Corp.: 20 employees
-   - Average Employment = (250000 + 269 + 456 + 20) / 4 ≈ 62731.25
-**Conclusion**: The category with the highest average employment is **OEM Supply Chain**, with an average of approximately 62,731 employees.</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="E65" t="b">
-        <v>1</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+- **OEM (Footprint)** includes Toyota Industries Group (TACG-TICA) and Trenton Pressing. The average employment is \((18100 + 350) / 2 = 9225\).
+- **Tier 2/3** includes Adient, with an employment of 180.
+- **Tier 1** includes Linde + Wiemann, with an employment of 515.
+- **OEM Supply Chain** includes WIKA USA, Valeo, Volvo Cars USA, and Wabash National Corp. The average employment is \((250000 + 269 + 456 + 20) / 4 = 62731\).
+The category with the highest average employment is **OEM Supply Chain** at an average of 62,731 employees.</t>
         </is>
       </c>
       <c r="G65" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="H65" t="b">
+        <v>1</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
         <v>0.1</v>
       </c>
-      <c r="H65" t="b">
-        <v>0</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
-        <v>0.09</v>
-      </c>
       <c r="K65" t="b">
+        <v>0</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N65" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3659,33 +4392,33 @@
           <t>Identify companies with Employment &gt;= 10,000 and list their Category and Classification</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>The companies in Georgia within the EV supply chain that have employment of 10,000 or more are:
+      <c r="C66" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Toyota Industries Group (TACG-TICA)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>The companies in Georgia's EV supply chain with employment of 10,000 or more are:
 - **Toyota Industries Group (TACG-TICA)**
-  - **Category:** OEM (Footprint)
-  - **Classification Method:** Public OEM footprint / supplier listing
+  - Category: OEM (Footprint)
+  - Classification Method: Public OEM footprint / supplier listing
 - **Yazaki North America**
-  - **Category:** OEM Footprint
-  - **Classification Method:** Public OEM footprint / supplier listing</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="E66" t="b">
-        <v>1</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+  - Category: OEM Footprint
+  - Classification Method: Public OEM footprint / supplier listing</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.09</v>
+        <v>1.95</v>
       </c>
       <c r="H66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3693,9 +4426,20 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="K66" t="b">
+        <v>0</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N66" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3709,27 +4453,27 @@
 which has the highest total Employment?</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Among the provided categories, **OEM (Footprint)** has the highest total employment. This is based on the data from TN Americas Holding Inc., which reports 19600 employees and Toyota Industries Group (TACG-TICA), with 18100 employees. Together, they sum up to 37700 employees in this category.</t>
-        </is>
+      <c r="C67" t="n">
+        <v>0.608</v>
       </c>
       <c r="D67" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="E67" t="b">
-        <v>1</v>
+        <v>0.597</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Trenton Pressing</t>
+        </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>Among the provided categories, the category **OEM (Footprint)** has the highest total employment. This is based on the data from TN Americas Holding Inc., which reports an employment of 19600 and Toyota Industries Group (TACG-TICA) with 18100 employees, both falling under the OEM (Footprint) category.</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.1</v>
+        <v>1.86</v>
       </c>
       <c r="H67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3740,6 +4484,17 @@
         <v>0.09</v>
       </c>
       <c r="K67" t="b">
+        <v>0</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N67" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3753,27 +4508,27 @@
 one county contains the largest share of that role's companies)?</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>The EV Supply Chain Role "General Automotive" is most concentrated in Troup County. This can be seen from multiple companies listed as having this role and located in Troup County: PPG Industries Inc., Stryten Energy, Linde + Wiemann (listed twice but relevant only once), and PAI Industries Inc.</t>
-        </is>
+      <c r="C68" t="n">
+        <v>0.587</v>
       </c>
       <c r="D68" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="E68" t="b">
-        <v>1</v>
+        <v>0.579</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>PPG Industries Inc.</t>
+        </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>The EV Supply Chain Role "General Automotive" is most concentrated in Troup County. This can be seen from multiple companies located there including PPG Industries Inc., Stryten Energy, Linde + Wiemann (mentioned twice but considered once), and PAI Industries Inc. All these companies have their primary facilities in Troup County and are categorized under the "General Automotive" role.</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.1</v>
+        <v>1.89</v>
       </c>
       <c r="H68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3784,6 +4539,17 @@
         <v>0.1</v>
       </c>
       <c r="K68" t="b">
+        <v>0</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N68" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3797,38 +4563,49 @@
 company for each such role.</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Toyota Industries Group (TACG-TICA)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>The EV Supply Chain Role of "Advanced electrical architecture for EVs" has only one company listed in the dataset:
-- Company: Yamaha Motor Manufacturing Corp.</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E69" t="b">
-        <v>1</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+- **Company:** Yamaha Motor Manufacturing Corp.</t>
         </is>
       </c>
       <c r="G69" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H69" t="b">
+        <v>1</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
         <v>0.11</v>
       </c>
-      <c r="H69" t="b">
-        <v>0</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="J69" t="n">
-        <v>0.1</v>
-      </c>
       <c r="K69" t="b">
+        <v>0</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N69" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3842,36 +4619,30 @@
 Georgia)? Provide the bottom 5 counties by company count.</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.534</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ADVICS Manufacturing Georgia LLC</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>Based on the provided context, the counties with the fewest companies are:
-1. Coweta County: Contains data for Dongwon Autopart Technology Georgia LLC (2 entries)
-2. Troup County: Contains data for ADVICS Manufacturing Georgia LLC (2 entries), Sejong Georgia LLC (2 entries), and Joon Georgia, Inc. (2 entries)
-However, the question asks for the bottom 5 counties by company count excluding rows with Location = Georgia. Since only two counties are mentioned in the context provided and none of them have a location specified as "Georgia," the relevant companies across these two counties are:
-- Coweta County: Dongwon Autopart Technology Georgia LLC
-- Troup County: ADVICS Manufacturing Georgia LLC, Sejong Georgia LLC, Joon Georgia, Inc.
-Given this information, there aren't enough unique counties to provide a bottom 5 list. Only two distinct counties with companies listed are provided in the context:
-1. Coweta County (1 company)
-2. Troup County (3 companies)
-Since only these two counties are mentioned and none of them meet the exclusion criteria specified ("Location = Georgia"), it's not possible to compile a list of bottom 5 counties as requested based on the given data.</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="E70" t="b">
-        <v>1</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+1. Troup County: Contains entries for ADVICS Manufacturing Georgia LLC and Sejong Georgia LLC (2 companies).
+2. Coweta County: Contains an entry for Dongwon Autopart Technology Georgia LLC (1 company).
+Since only two counties are mentioned in the provided context, they cannot be ranked further to provide a bottom 5 list. However, Troup County has more entries than Coweta County specifically regarding these companies.</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.09</v>
+        <v>2.28</v>
       </c>
       <c r="H70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3882,6 +4653,17 @@
         <v>0.09</v>
       </c>
       <c r="K70" t="b">
+        <v>0</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N70" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3895,27 +4677,27 @@
 supplier.</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>For Tier 1 suppliers in Georgia's EV supply chain, Carroll County has only one Tier 1 supplier, which is Haering Precision USA LP. However, upon closer inspection of the provided context, Haering Precision USA LP is listed as a Tier 2/3 supplier located in Carroll County. Therefore, based on the given information, there are no counties with only one Tier 1 supplier according to the strict categorization criteria provided.</t>
-        </is>
+      <c r="C71" t="n">
+        <v>0.547</v>
       </c>
       <c r="D71" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E71" t="b">
-        <v>1</v>
+        <v>0.54</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Linde + Wiemann</t>
+        </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>In Troup County, there is only one Tier 1 supplier named Stryten Energy. However, upon closer inspection of the provided sources, it appears there are multiple Tier 1 suppliers listed for Troup County (Linde + Wiemann, PPG Industries Inc., and Sejong Georgia LLC). Therefore, no single Tier 1 supplier exists uniquely in a county based on the given information.</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.1</v>
+        <v>1.92</v>
       </c>
       <c r="H71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3923,9 +4705,20 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="K71" t="b">
+        <v>0</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N71" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3939,30 +4732,30 @@
 distinct EV Supply Chain Roles recorded.</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>The company ZF Gainesville LLC appears multiple times in the dataset with distinct EV Supply Chain Roles:
-1. **EV thermal management and power electronics**
-2. **EV body, powertrain, and thermal components**
-3. **EV thermal systems and electronics**</t>
-        </is>
+      <c r="C72" t="n">
+        <v>0.606</v>
       </c>
       <c r="D72" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="E72" t="b">
-        <v>1</v>
+        <v>0.603</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Toyota Industries Group (TACG-TICA)</t>
+        </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>The company that appears multiple times in the dataset is ZF Gainesville LLC. The distinct EV Supply Chain Roles recorded for this company are:
+1. EV thermal management and power electronics
+2. EV body, powertrain, and thermal components
+3. EV thermal systems and electronics</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.13</v>
+        <v>1.59</v>
       </c>
       <c r="H72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3973,6 +4766,17 @@
         <v>0.09</v>
       </c>
       <c r="K72" t="b">
+        <v>0</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N72" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3986,38 +4790,34 @@
 Supply Chain Roles, and Locations.</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>For ZF Gainesville LLC, comparing across different sources:
-- **Category**: 
-  - Source 1 &amp; 3: OEM Footprint
-  - Sources 2, 4, 5, 6: OEM Supply Chain
-- **EV Supply Chain Role**:
-  - Source 1: EV thermal management and power electronics
-  - Source 2: EV body, powertrain, and thermal components
-  - Source 3: EV thermal systems and electronics
-  - Sources 4 &amp; 5: EV body, powertrain, and thermal components (Source 4) / EV thermal management and power electronics (Source 5)
-  - Source 6: EV thermal systems and electronics
-- **Location**: Georgia (all sources)
-ZF Gainesville LLC is consistently listed as being located in Georgia across all provided sources. The company's category varies between OEM Supply Chain and OEM Footprint, while its role within the EV supply chain includes thermal management, powertrain components, body parts, and electronics, with slight variations depending on the source.</t>
-        </is>
+      <c r="C73" t="n">
+        <v>1.161</v>
       </c>
       <c r="D73" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="E73" t="b">
-        <v>1</v>
+        <v>1.154</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ZF Gainesville LLC</t>
+        </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>For ZF Gainesville LLC, the provided sources indicate variations in categories, EV supply chain roles, and locations as follows:
+1. **Category**: OEM Supply Chain (Sources 1, 2, 4, 5), OEM Footprint (Sources 3, 6)
+2. **EV Supply Chain Role**:
+   - EV thermal management and power electronics (Sources 1, 5)
+   - EV body, powertrain, and thermal components (Sources 2, 4)
+   - EV thermal systems and electronics (Sources 3, 6)
+3. **Location**: Georgia (All sources)
+These variations reflect different aspects of the company's operations within the electric vehicle supply chain in Georgia.</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.1</v>
+        <v>3.12</v>
       </c>
       <c r="H73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4025,9 +4825,20 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>0.09</v>
+        <v>0.19</v>
       </c>
       <c r="K73" t="b">
+        <v>0</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N73" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4041,7 +4852,18 @@
 recorded.</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Novelis Inc.</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>For Novelis Inc., the different locations and primary facility types recorded are:
 - **Gainesville, Hall County**: Manufacturing Plant (Motor vehicle transmissions)
@@ -4049,22 +4871,11 @@
 - **Lawrenceville, Gwinnett County**: Manufacturing Plant (Acoustic and thermally effective automotive components)</t>
         </is>
       </c>
-      <c r="D74" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E74" t="b">
-        <v>1</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
       <c r="G74" t="n">
-        <v>0.1</v>
+        <v>1.88</v>
       </c>
       <c r="H74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4072,9 +4883,20 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K74" t="b">
+        <v>0</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4088,33 +4910,33 @@
 associated Location.</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Sewon America Inc.</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>For Sewon America Inc., the recorded products/services and their associated locations are:
 1. **Product/Service:** Fire truck bodies  
-   - **Location:** Marietta, Cobb County
+   **Location:** Marietta, Cobb County
 2. **Product/Service:** Automotive aftermarket parts  
-   - **Location:** Atlanta, Fulton County
+   **Location:** Atlanta, Fulton County
 3. **Product/Service:** Motor vehicle engines and parts  
-   - **Location:** Athens, Clarke County</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="E75" t="b">
-        <v>1</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+   **Location:** Athens, Clarke County</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.1</v>
+        <v>1.87</v>
       </c>
       <c r="H75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4125,6 +4947,17 @@
         <v>0.09</v>
       </c>
       <c r="K75" t="b">
+        <v>0</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N75" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4138,30 +4971,32 @@
 Group names.</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>The Industry Group that has both Tier 1 and Tier 2/3 suppliers present is "Rubber and Miscellaneous Plastic Products." This group includes Bosch (Automotive Division) as a Tier 2/3 supplier in Thomson, McDuffie County. However, there is no Tier 1 supplier listed under this specific category in the provided context.
-Additionally, the Industry Group "Machinery Except Electrical" has a Tier 2/3 supplier: Haering Precision USA LP located in Carroll County. There is no Tier 1 supplier mentioned for this group either within the given information.
-The closest match to having both tiers represented would be "Transportation Equipment," which includes PPG Industries Inc. as a Tier 1 supplier, but there are no Tier 2/3 suppliers listed under this category based on the provided context.
-Therefore, strictly adhering to the exact Industry Groups with companies mentioned in the context and their respective tier classifications, only "Rubber and Miscellaneous Plastic Products" has a Tier 2/3 supplier (Bosch Automotive Division) explicitly noted.</t>
-        </is>
+      <c r="C76" t="n">
+        <v>0.554</v>
       </c>
       <c r="D76" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="E76" t="b">
-        <v>1</v>
+        <v>0.547</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Bosch (Automotive Division)</t>
+        </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>The Industry Group that has both Tier 1 and Tier 2/3 suppliers present is **Transportation Equipment**. 
+- **Tier 1 Supplier**: PPG Industries Inc.
+- **Tier 2/3 Suppliers**: Bosch (Automotive Division) falls under this category, although it's listed twice with similar information but no specific tier designation change in the provided context.
+Additionally, another Industry Group that fits is **Rubber and Miscellaneous Plastic Products**:
+- **Tier 2/3 Supplier**: Bosch (Automotive Division)
+However, based on the exact match of both tiers within a single group as per the given data, **Transportation Equipment** is the primary answer.</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.1</v>
+        <v>2.98</v>
       </c>
       <c r="H76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4169,9 +5004,20 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K76" t="b">
+        <v>0</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N76" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4185,37 +5031,48 @@
 what are the companies?</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>The county with the highest number of Materials entries is Bulloch County. The company in this category is Ascend Elements.</t>
-        </is>
+      <c r="C77" t="n">
+        <v>0.523</v>
       </c>
       <c r="D77" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E77" t="b">
-        <v>1</v>
+        <v>0.517</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Ascend Elements</t>
+        </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>The county with the highest number of Materials entries is Bulloch County. The company in this category is Ascend Elements, which provides interior and exterior plastic parts for the automotive industry.</t>
         </is>
       </c>
       <c r="G77" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H77" t="b">
+        <v>1</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K77" t="b">
+        <v>0</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
         <v>0.1</v>
       </c>
-      <c r="H77" t="b">
-        <v>0</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="J77" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="K77" t="b">
+      <c r="N77" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4229,32 +5086,31 @@
 each of those roles per county?</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Battery Pack or Battery Cell activities are present in two counties based on the provided context:
+      <c r="C78" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>FREYR Battery</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Battery Pack or Battery Cell activities are present in two counties:
 1. **Bryan County**: 
    - 1 company (Honda Development &amp; Manufacturing) involved in Battery Cells for electric mobility with employment of 400 people.
 2. **Coweta County**:
-   - 1 company (Hitachi Astemo Americas Inc.) involved in Battery Cells for electric mobility with employment of 723 people.
-No companies are listed as directly involved in Battery Pack activities based on the given information.</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="E78" t="b">
-        <v>1</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+   - 1 company (Hitachi Astemo Americas Inc.) involved in Battery Cells for electric mobility with employment of 723 people.</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.11</v>
+        <v>2.02</v>
       </c>
       <c r="H78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4262,9 +5118,20 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="K78" t="b">
+        <v>0</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N78" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4278,30 +5145,30 @@
 Tier 1/2; list them with their Product / Service.</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Hitachi Astemo Americas Inc.</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>The companies marked as EV / Battery Relevant = No but still categorized as Tier 1 or Tier 1/2 are:
-- FREYR Battery | Product / Service: Decorative and functional coating systems
-- SK Battery America | Product / Service: Engineered steel systems mounted in motor vehicles
-- Hyundai &amp; LG Energy Solution (LGES) | Product / Service: Storage batteries</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="E79" t="b">
-        <v>1</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+- **FREYR Battery**: Product / Service: Decorative and functional coating systems.
+- **SK Battery America**: Product / Service: Engineered steel systems mounted in motor vehicles.
+- **Hyundai &amp; LG Energy Solution (LGES)**: Product / Service: Storage batteries.</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.11</v>
+        <v>2.05</v>
       </c>
       <c r="H79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4312,6 +5179,17 @@
         <v>0.09</v>
       </c>
       <c r="K79" t="b">
+        <v>0</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N79" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4325,34 +5203,40 @@
 fall under each?</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>The Supplier or Affiliation Type categories that exist in the dataset are "Automotive supply chain participant" and no other types. There are six companies falling under this category:
-1. Adient
-2. Haering Precision USA LP
-3. Robert Bosch LLC
-4. Toyota Industries Group (TACG-TICA) - although it is listed twice, both instances fall under the OEM category rather than a supplier affiliation.
-5. Vista Metals Corp.
-6. Vanguard National Trailer Corp.
-Note: The second instance of "Toyota Industries Group (TACG-TICA)" does not change the count as it too falls under the OEM category and not as an automotive supply chain participant.</t>
-        </is>
+      <c r="C80" t="n">
+        <v>0.5629999999999999</v>
       </c>
       <c r="D80" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="E80" t="b">
-        <v>1</v>
+        <v>0.552</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Toyota Industries Group (TACG-TICA)</t>
+        </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>In the provided dataset, there are two Supplier or Affiliation Type categories:
+1. **Automotive supply chain participant**: This category includes 6 companies:
+   - Adient
+   - Haering Precision USA LP
+   - Robert Bosch LLC
+   - Trenton Pressing (Note: Although Trenton Pressing's primary role is OEM corporate footprint and supplier integration, it also participates in the automotive supply chain.)
+   - Vista Metals Corp.
+   - Vanguard National Trailer Corp.
+2. **OEM**: This category includes 2 companies:
+   - Toyota Industries Group (TACG-TICA) appears twice but represents a single entity with different roles described.
+   - Trenton Pressing is also listed under OEM corporate footprint, indicating its role as an OEM in addition to being part of the supply chain.
+However, if we are strictly categorizing based on the "Supplier or Affiliation Type" field and excluding repeated entries or secondary classifications:
+- **Automotive supply chain participant**: 6 companies
+- **OEM**: 1 company (Toyota Industries Group)</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.12</v>
+        <v>4.4</v>
       </c>
       <c r="H80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4363,6 +5247,17 @@
         <v>0.11</v>
       </c>
       <c r="K80" t="b">
+        <v>0</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N80" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4376,34 +5271,34 @@
 EV Supply Chain Roles are represented?</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Among the entries listed for Georgia EV supply chain companies, the following EV Supply Chain Roles are represented by companies that fall under the category of OEM Supply Chain:
+      <c r="C81" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ZF Gainesville LLC</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Among the entries provided for Georgia EV supply chain companies, the following EV Supply Chain Roles are represented by companies affiliated with Original Equipment Manufacturers (OEMs):
 1. **EV body, powertrain, and thermal components** - ZF Gainesville LLC
 2. **Body and chassis components for EV and ICE OEMs** - Vanguard National Trailer Corp.
 3. **EV wiring harnesses and power distribution** - Woodbridge Foam Corp.
 4. **Advanced electrical architecture for EVs** - Yamaha Motor Manufacturing Corp.
 5. **EV thermal management and power electronics** - ZF Gainesville LLC
 6. **High-voltage EV connectors and electronics** - Woory Industrial Co.
-These roles are critical components in the electric vehicle supply chain, covering areas such as structural integrity, electrical systems, and thermal management.</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="E81" t="b">
-        <v>1</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+These roles are cited based on the companies' specific contributions to the electric vehicle supply chain as detailed in the provided context.</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.1</v>
+        <v>3.41</v>
       </c>
       <c r="H81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4411,9 +5306,20 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="K81" t="b">
+        <v>0</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N81" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4427,33 +5333,33 @@
 have?</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Based on the provided context, there are no companies listed as having missing Primary OEMs. However, if you're asking about the EV Supply Chain Roles of the mentioned companies in Georgia:
-- ZF Gainesville LLC has roles related to EV body, powertrain, and thermal components, as well as EV thermal management and power electronics.
-- Vanguard National Trailer Corp.'s role is body and chassis components for both EV and ICE OEMs.
-- Woory Industrial Co. provides high-voltage EV connectors and electronics.
-- Vista Metals Corp. manufactures EV and ICE component parts.
-- Yamaha Motor Manufacturing Corp. focuses on advanced electrical architecture for EVs.
-TN Americas Holding Inc. appears twice but does not have a missing Primary OEM, it is listed as an OEM parent group footprint (EV + HD electrification).</t>
-        </is>
+      <c r="C82" t="n">
+        <v>0.634</v>
       </c>
       <c r="D82" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="E82" t="b">
-        <v>1</v>
+        <v>0.629</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>ZF Gainesville LLC</t>
+        </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>Based on the provided context, none of the listed Georgia EV supply chain companies are noted as having missing Primary OEMs. However, the question seems to imply identifying companies without explicitly named primary Original Equipment Manufacturers (OEMs), which would mean focusing on their roles directly:
+- **Vanguard National Trailer Corp.** has an EV Supply Chain Role of body and chassis components for both EV and ICE OEMs.
+- **Woory Industrial Co.** provides high-voltage EV connectors and electronics.
+- **ZF Gainesville LLC** (listed twice but with different focus areas) is involved in EV body, powertrain, and thermal components as well as EV thermal management and power electronics.
+- **Vista Metals Corp.** manufactures EV and ICE component parts.
+- **Yamaha Motor Manufacturing Corp.** focuses on advanced electrical architecture for EVs.
+These companies are directly engaged in the EV supply chain without a specific primary OEM listed, meaning they serve multiple or unspecified OEMs within their roles.</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.11</v>
+        <v>3.97</v>
       </c>
       <c r="H82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4464,6 +5370,17 @@
         <v>0.09</v>
       </c>
       <c r="K82" t="b">
+        <v>0</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N82" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4477,27 +5394,27 @@
 Supply Chain Role and Location.</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>None of the provided company entries mention "lithium" in their Product / Service descriptions. Therefore, there are no companies listed that fit the criteria specified in the question.</t>
-        </is>
+      <c r="C83" t="n">
+        <v>0.613</v>
       </c>
       <c r="D83" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E83" t="b">
-        <v>1</v>
+        <v>0.612</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>FREYR Battery</t>
+        </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>None of the provided context mentions any company with "Product / Service" text that includes the word "lithium." Therefore, there are no companies listed in the given information that meet this criterion.</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="H83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4505,9 +5422,20 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K83" t="b">
+        <v>0</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N83" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4521,37 +5449,48 @@
 Categories?</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>None of the provided companies are described as recyclers in their product or service offerings. All the listed companies fall under categories such as OEM Supply Chain or OEM (Footprint) and provide services related to manufacturing components for automotive and industrial applications rather than recycling.</t>
-        </is>
+      <c r="C84" t="n">
+        <v>0.451</v>
       </c>
       <c r="D84" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="E84" t="b">
-        <v>1</v>
+        <v>0.431</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Wheelabrator Group Inc.</t>
+        </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>None of the provided companies in the context are described as recyclers in their Product/Service details. All listed companies deal with manufacturing or supply chain roles related to automotive components, metal stamping, textiles for interiors, and commercial vehicle operations. There is no mention of recycling activities among these firms. Therefore, there are no relevant companies fitting the criteria specified in the question.</t>
         </is>
       </c>
       <c r="G84" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H84" t="b">
+        <v>1</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
         <v>0.1</v>
       </c>
-      <c r="H84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="J84" t="n">
-        <v>0.09</v>
-      </c>
       <c r="K84" t="b">
+        <v>0</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N84" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4565,34 +5504,34 @@
 provide their Primary OEMs.</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>The companies that provide wiring harness-related products/services are:
+      <c r="C85" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Woodbridge Foam Corp.</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>The companies that provide wiring harness-related products/services in Georgia are:
 1. **Woodbridge Foam Corp.**
    - EV Supply Chain Role: EV wiring harnesses and power distribution
    - Product / Service: Automotive wiring harnesses &amp; electrical distribution systems
 2. **WIKA USA**
    - EV Supply Chain Role: HV and LV wiring harnesses for EVs and ICE vehicles
    - Product / Service: Vehicle power &amp; data solutions; wiring harnesses and connectors
-Neither of these companies specifies a Primary OEM in the provided context.</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="E85" t="b">
-        <v>1</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+Neither of these companies specifically mentions primary OEMs in the provided context.</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0.1</v>
+        <v>2.51</v>
       </c>
       <c r="H85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4600,9 +5539,20 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="K85" t="b">
+        <v>0</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N85" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4616,27 +5566,27 @@
 Relevant status?</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>The companies that mention 'connectors' in their Product / Service description are Woory Industrial Co., which has an "EV / Battery Relevant" status of Yes.</t>
-        </is>
+      <c r="C86" t="n">
+        <v>0.579</v>
       </c>
       <c r="D86" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E86" t="b">
-        <v>1</v>
+        <v>0.554</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Woory Industrial Co.</t>
+        </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>The companies that mention 'connectors' in their Product / Service description are Woory Industrial Co. Both instances of Woory Industrial Co. list connectors as part of their product/service offerings and have an EV / Battery Relevant status of "Yes".</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>0.1</v>
+        <v>1.4</v>
       </c>
       <c r="H86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4644,9 +5594,20 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K86" t="b">
+        <v>0</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="N86" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4660,31 +5621,31 @@
 Chain Role and Primary Facility Type.</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ZF Gainesville LLC</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>The companies whose Product / Service mentions 'thermal' are:
 1. **ZF Gainesville LLC**
    - **EV Supply Chain Role:** EV thermal management and power electronics | EV thermal systems and electronics
    - **Primary Facility Type:** Manufacturing | Engineering / Operations
-No other company in the provided context meets this criterion.</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E87" t="b">
-        <v>1</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+No other company in the provided context mentions 'thermal' in their product or service description.</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>0.1</v>
+        <v>1.8</v>
       </c>
       <c r="H87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4692,9 +5653,20 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="K87" t="b">
+        <v>0</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N87" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4708,7 +5680,18 @@
 Category and Location.</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>TCI Powder Coatings</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>The company that provides powder coatings as part of its product/service is:
 - **Company:** TCI Powder Coatings  
@@ -4716,22 +5699,11 @@
   **Location:** Troup County</t>
         </is>
       </c>
-      <c r="D88" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E88" t="b">
-        <v>1</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
       <c r="G88" t="n">
-        <v>0.11</v>
+        <v>1.18</v>
       </c>
       <c r="H88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4739,9 +5711,20 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="K88" t="b">
+        <v>0</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M88" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N88" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4755,27 +5738,27 @@
 are they assigned?</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>The company that mentions 'sensors' in its Product/Service description is Woory Industrial Co. Its EV Supply Chain Role is "High-voltage EV connectors and electronics."</t>
-        </is>
+      <c r="C89" t="n">
+        <v>0.601</v>
       </c>
       <c r="D89" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Woory Industrial Co.</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>The company that mentions "sensors" in its Product/Service description is Woory Industrial Co. Its EV Supply Chain Role is "High-voltage EV connectors and electronics."</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
         <v>1.08</v>
       </c>
-      <c r="E89" t="b">
-        <v>1</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="G89" t="n">
-        <v>0.1</v>
-      </c>
       <c r="H89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4783,9 +5766,20 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="K89" t="b">
+        <v>0</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M89" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N89" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4799,7 +5793,18 @@
 by Employment within each method.</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Toyota Industries Group (TACG-TICA)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>**Classification Method: Public OEM footprint / supplier listing**
 - **Number of Companies:** 4
@@ -4807,33 +5812,20 @@
   1. Toyota Industries Group (TACG-TICA) - 18,100 employees
   2. Vista Metals Corp. - 1,500 employees
   3. Trenton Pressing - 350 employees
-(Note: Only three companies are listed here as there are fewer than five companies under this classification method.)
 **Classification Method: Supplier**
 - **Number of Companies:** 4
 - **Top 5 by Employment:**
   1. Linde + Wiemann - 515 employees
   2. NIFCO KTW America Corp. - 300 employees
   3. Adient - 180 employees
-  4. Haering Precision USA LP - 200 employees
-(Note: All four companies are listed as they all fall under this classification method.)</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="E90" t="b">
-        <v>1</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+  4. Haering Precision USA LP - 200 employees</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.09</v>
+        <v>3.64</v>
       </c>
       <c r="H90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4844,6 +5836,17 @@
         <v>0.11</v>
       </c>
       <c r="K90" t="b">
+        <v>0</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N90" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4857,13 +5860,24 @@
 Categories and EV / Battery Relevant status.</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>The entries classified as 'Public OEM footprint / supplier listing' with their categories and EV/Battery Relevant statuses are:
+      <c r="C91" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>TN Americas Holding Inc.</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Entries classified as 'Public OEM footprint / supplier listing' include the following companies with their respective categories and EV/Battery Relevant statuses:
 1. **TN Americas Holding Inc.**
    - Category: OEM (Footprint)
    - EV/Battery Relevant: Yes
-2. **ZF Gainesville LLC** (two listings, but both relevant)
+2. **ZF Gainesville LLC** (two entries, but both relevant to EV supply chain)
    - Category: OEM Footprint
    - EV/Battery Relevant: Yes
    - Category: OEM Supply Chain
@@ -4885,22 +5899,11 @@
    - EV/Battery Relevant: Yes</t>
         </is>
       </c>
-      <c r="D91" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="E91" t="b">
-        <v>1</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
       <c r="G91" t="n">
-        <v>0.1</v>
+        <v>4.72</v>
       </c>
       <c r="H91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -4908,9 +5911,20 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K91" t="b">
+        <v>0</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N91" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4924,7 +5938,18 @@
 do they cover?</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Woory Industrial Co.</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>Based on the provided context, the companies classified as Direct Manufacturers in Georgia's EV supply chain and their respective roles are:
 1. **Woory Industrial Co.**
@@ -4933,37 +5958,37 @@
    - **EV Supply Chain Role:** EV wiring harnesses and power distribution
 3. **ZF Gainesville LLC**
    - **EV Supply Chain Role:** EV thermal management and power electronics
-   - Additionally, ZF Gainesville LLC is involved in EV body, powertrain, and thermal components.
+   - Additionally, ZF Gainesville LLC also covers EV body, powertrain, and thermal components.
 4. **Yamaha Motor Manufacturing Corp.**
    - **EV Supply Chain Role:** Advanced electrical architecture for EVs</t>
         </is>
       </c>
-      <c r="D92" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="E92" t="b">
-        <v>1</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
       <c r="G92" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="H92" t="b">
+        <v>1</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
         <v>0.1</v>
       </c>
-      <c r="H92" t="b">
-        <v>0</v>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="J92" t="n">
-        <v>0.09</v>
-      </c>
       <c r="K92" t="b">
+        <v>0</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N92" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4977,27 +6002,27 @@
 frequently?</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Vanguard National Trailer Corp.</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>Among the companies classified as Supplier in Georgia's EV supply chain, the role of "EV thermal management and power electronics" appears most frequently. This is evident from ZF Gainesville LLC being listed twice with this specific role.</t>
         </is>
       </c>
-      <c r="D93" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="E93" t="b">
-        <v>1</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
       <c r="G93" t="n">
-        <v>0.1</v>
+        <v>1.33</v>
       </c>
       <c r="H93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5008,6 +6033,17 @@
         <v>0.09</v>
       </c>
       <c r="K93" t="b">
+        <v>0</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M93" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N93" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5021,7 +6057,18 @@
 Supplier or Affiliation Type is not filled; list those companies.</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Vista Metals Corp.</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>The companies that have a Category indicating an OEM-related classification but do not fill in the Supplier or Affiliation Type are:
 1. Vista Metals Corp.
@@ -5030,25 +6077,14 @@
 4. Yamaha Motor Manufacturing Corp.
 5. Toyota Industries Group (TACG-TICA)
 6. Vernay
-These companies all have a Category that starts with "OEM" but do not specify a Supplier or Affiliation Type in the provided information.</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="E94" t="b">
-        <v>1</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+These companies all have a Category starting with 'OEM' and do not specify a Supplier or Affiliation Type in the provided context.</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0.09</v>
+        <v>2.27</v>
       </c>
       <c r="H94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5056,9 +6092,20 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="K94" t="b">
+        <v>0</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N94" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5072,37 +6119,48 @@
 include companies in this dataset?</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>The provided context does not specify an exact minimum employment threshold for including companies in the dataset. However, it lists several companies with varying numbers of employees, indicating that there isn't a uniform cutoff based on the given information alone. Companies listed range from 20 employees (Wabash National Corp.) to over 173,700 employees (Yachiyo Manufacturing of America LLC), suggesting that employment size is not a strict criterion for inclusion in this dataset according to the provided context.</t>
-        </is>
+      <c r="C95" t="n">
+        <v>0.342</v>
       </c>
       <c r="D95" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E95" t="b">
-        <v>1</v>
+        <v>0.311</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Toyota Industries Group (TACG-TICA)</t>
+        </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>The provided context does not specify an exact minimum employment threshold for including companies in the dataset. However, it lists several companies with varying numbers of employees, indicating that there isn't a uniform low number set as a strict threshold since even small-scale operations like Wabash National Corp. (20 employees) are included alongside larger entities such as Toyota Industries Group (18100 employees). Therefore, based on the given information, no specific minimum employment threshold can be cited directly from the provided data.</t>
         </is>
       </c>
       <c r="G95" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H95" t="b">
+        <v>1</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K95" t="b">
+        <v>0</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
         <v>0.1</v>
       </c>
-      <c r="H95" t="b">
-        <v>0</v>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="J95" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="K95" t="b">
+      <c r="N95" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5116,32 +6174,32 @@
 values standardized?</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Trenton Pressing</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>According to the provided context, the Location field includes both city and county information. For example:
 - **Trenton Pressing**: Located in Georgia (no specific city mentioned).
 - **Linde + Wiemann**: Located in Troup County.
 - **First American Resources**: Located in Albany, Dougherty County.
 - **TI Fluid Systems**: Located in Atlanta, Fulton County.
-City values are standardized by including the county name when applicable. For instance, First American Resources is listed as being located in "Albany, Dougherty County," and TI Fluid Systems is listed as being in "Atlanta, Fulton County."</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="E96" t="b">
-        <v>1</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+The City values are standardized by including the county name when applicable. For instance, "Atlanta, Fulton County" provides both city and county information clearly.</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0.72</v>
+        <v>2.43</v>
       </c>
       <c r="H96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -5152,6 +6210,17 @@
         <v>0.09</v>
       </c>
       <c r="K96" t="b">
+        <v>0</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M96" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N96" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5165,32 +6234,32 @@
 Role (list the roles mentioned in the definition)?</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>The context provided mentions several roles within the EV supply chain. The controlled vocabulary for EV Supply Chain Role includes:
-1. **EV thermal management and power electronics** - ZF Gainesville LLC
-2. **EV wiring harnesses and power distribution** - Woodbridge Foam Corp.
-3. **EV body, powertrain, and thermal components** - ZF Gainesville LLC
-4. **High-voltage EV connectors and electronics** - Woory Industrial Co.
-These roles are specific to the companies mentioned in the context and relate directly to their contributions within the electric vehicle supply chain.</t>
-        </is>
+      <c r="C97" t="n">
+        <v>0.535</v>
       </c>
       <c r="D97" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="E97" t="b">
-        <v>1</v>
+        <v>0.526</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>ZF Gainesville LLC</t>
+        </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>The context provided mentions several roles within the EV supply chain. The roles explicitly listed are:
+1. **EV thermal management and power electronics**
+2. **EV wiring harnesses and power distribution**
+3. **EV body, powertrain, and thermal components**
+4. **High-voltage EV connectors and electronics**
+These roles are associated with companies such as ZF Gainesville LLC, Woodbridge Foam Corp., Woory Industrial Co., and TI Fluid Systems in the context of Georgia's EV supply chain.</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0.51</v>
+        <v>2.28</v>
       </c>
       <c r="H97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -5201,6 +6270,17 @@
         <v>0.09</v>
       </c>
       <c r="K97" t="b">
+        <v>0</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M97" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N97" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5214,9 +6294,20 @@
 Supply Chain Role.</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>The companies in Georgia with the Category "OEM Footprint" are:
+      <c r="C98" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>TN Americas Holding Inc.</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>The companies listed under the category "OEM (Footprint)" with their employment numbers and EV Supply Chain Roles are:
 1. **TN Americas Holding Inc.**
    - Employment: 19600
    - EV Supply Chain Role: OEM parent group footprint (EV + HD electrification)
@@ -5228,32 +6319,32 @@
    - EV Supply Chain Role: OEM corporate footprint and supplier integration</t>
         </is>
       </c>
-      <c r="D98" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E98" t="b">
-        <v>1</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
       <c r="G98" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H98" t="b">
+        <v>1</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K98" t="b">
+        <v>0</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M98" t="n">
         <v>0.1</v>
       </c>
-      <c r="H98" t="b">
-        <v>0</v>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="J98" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="K98" t="b">
+      <c r="N98" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5267,30 +6358,30 @@
 their Categories and Locations?</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Trenton Pressing</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>The company with Primary Facility Type = Regional corporate operations is:
 - **Trenton Pressing**
-  - Category: OEM (Footprint)
-  - Location: Georgia</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E99" t="b">
-        <v>1</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+  - **Category:** OEM (Footprint)
+  - **Location:** Georgia</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.1</v>
+        <v>1.22</v>
       </c>
       <c r="H99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5301,6 +6392,17 @@
         <v>0.09</v>
       </c>
       <c r="K99" t="b">
+        <v>0</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M99" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N99" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5314,7 +6416,18 @@
 how many companies are in each?</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Hitachi Astemo Americas Inc.</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>Among the EV/Battery Relevant = Yes companies listed:
 - **Electronic and Other Electrical Equipment and Components**: 1 company (Hitachi Astemo Americas Inc.)
@@ -5325,22 +6438,11 @@
 - **Automotive electronics**: 1 company (Yamaha Motor Manufacturing Corp.)</t>
         </is>
       </c>
-      <c r="D100" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E100" t="b">
-        <v>1</v>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
       <c r="G100" t="n">
-        <v>0.1</v>
+        <v>2.84</v>
       </c>
       <c r="H100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5351,6 +6453,17 @@
         <v>0.09</v>
       </c>
       <c r="K100" t="b">
+        <v>0</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M100" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N100" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5364,27 +6477,27 @@
 and Components, and list their Product / Service.</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Within the Tier 1 suppliers listed, Woory Industrial Co. is the company that falls under the category of 'Electronic and Other Electrical Equipment and Components.' Their product/service includes automotive connectors, terminals, sensors, and power/data components.</t>
-        </is>
+      <c r="C101" t="n">
+        <v>0.5629999999999999</v>
       </c>
       <c r="D101" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="E101" t="b">
-        <v>1</v>
+        <v>0.554</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Linde + Wiemann</t>
+        </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>Within Tier 1 suppliers, the company in the category of 'Electronic and Other Electrical Equipment and Components' is Woory Industrial Co. Their product/service includes automotive connectors, terminals, sensors, and power/data components.</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>0.11</v>
+        <v>1.31</v>
       </c>
       <c r="H101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5392,9 +6505,20 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K101" t="b">
+        <v>0</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M101" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N101" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5408,30 +6532,30 @@
 described)?</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>According to the provided context, the methodology for assigning supply chain tiers appears to be based on the company's role within the automotive industry and its direct or indirect relevance to EV components. Companies are categorized as Tier 1 if they provide general automotive parts or services to multiple OEMs, while companies like Haering Precision USA LP and Bosch (Automotive Division) are classified as Tier 2/3 due to their more specialized roles such as providing tools and dies for the automotive industry or custom injection molded plastic products. This classification is indicated by the "Category" field in each source entry.
-For example:
-- **Tier 1**: Valeo, Linde + Wiemann, PPG Industries Inc., Robert Bosch LLC
-- **Tier 2/3**: Haering Precision USA LP, Bosch (Automotive Division)</t>
-        </is>
+      <c r="C102" t="n">
+        <v>0.362</v>
       </c>
       <c r="D102" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="E102" t="b">
-        <v>1</v>
+        <v>0.35</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Valeo</t>
+        </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+          <t>According to the provided context, supply chain tiers are assigned based on the company's role in the automotive industry. Specifically:
+- **Tier 1**: Companies that directly supply components or systems to Original Equipment Manufacturers (OEMs). For example, Linde + Wiemann and Robert Bosch LLC are categorized as Tier 1 suppliers providing general automotive parts like transmissions and powertrain systems.
+- **Tier 2/3**: Companies that supply tools, dies, or materials used in the production of components for OEMs. Haering Precision USA LP is an example of a Tier 2/3 supplier that provides tools and dies for the automotive industry.
+The classification method described involves identifying whether companies are direct suppliers to OEMs (Tier 1) or provide indirect support through manufacturing aids and materials (Tier 2/3).</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0.1</v>
+        <v>3.43</v>
       </c>
       <c r="H102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5442,6 +6566,17 @@
         <v>0.1</v>
       </c>
       <c r="K102" t="b">
+        <v>0</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M102" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="N102" t="b">
         <v>0</v>
       </c>
     </row>

--- a/test_results_all_101.xlsx
+++ b/test_results_all_101.xlsx
@@ -544,13 +544,13 @@
 - Linde + Wiemann
 - Stryten Energy
 - Robert Bosch LLC
-**Tier 1 Company with EV Battery Relevant Role:**
+**Tier 1 Company with EV/Battery Relevant Role:**
 - Valeo (EV Supply Chain Role: Tier 1 automotive components, EV / Battery Relevant: Yes)
-Note: No companies are categorized as both Tier 1 and Tier 2/3 in the provided context.</t>
+Note: No companies are categorized as Tier 1/2 in the provided context.</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4.9</v>
+        <v>4.61</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.26</v>
+        <v>0.14</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -602,15 +602,15 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>The company involved in Battery Pack activities is:
-- **Hyundai Motor Group**
-  - **Category:** Tier 1/2
-  - **Location:** McDonough, Henry County
-  - **Product / Service:** Battery parts for electric vehicles
-  - **Employment:** 164</t>
+- **Company:** Hyundai Motor Group  
+  **Category:** Tier 1/2  
+  **Location:** McDonough, Henry County  
+  **Product / Service:** Battery parts for electric vehicles  
+  **Employment:** 164</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -621,18 +621,18 @@
         </is>
       </c>
       <c r="J3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
         <v>0.11</v>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>0.1</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -719,12 +719,12 @@
           <t>The company involved in thermal management for the EV supply chain in Georgia is:
 - **ZF Gainesville LLC**
   - Location: Georgia
-  - Primary Facility Type: Manufacturing (for one entry) / Engineering / Operations (for another entry)
-This company plays a significant role in providing EV thermal management and power electronics, contributing to the state's EV supply chain capabilities.</t>
+  - Primary Facility Type: Manufacturing (for one listing) / Engineering / Operations (for another listing)
+No other companies listed have a primary role specifically designated as thermal management within the EV supply chain.</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -775,17 +775,15 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>The companies tagged as Power Electronics in Georgia's EV supply chain and their respective products/services are:
-1. **Woory Industrial Co.**
-   - **Product/Service:** Automotive connectors, terminals, sensors, and power/data components
-2. **Yazaki North America**
-   - **Product/Service:** Automotive supplier division (mobility solutions: ADAS, powertrain, electronics)
-3. **ZF Gainesville LLC**
-   - **Product/Service:** Automotive supplier footprint (electrification, thermal, powertrain, ADAS components)</t>
+          <t>The companies tagged as providing power electronics in Georgia's EV supply chain are Woory Industrial Co., Yazaki North America, ZF Gainesville LLC, and Yamaha Motor Manufacturing Corp. 
+- **Woory Industrial Co.** provides automotive connectors, terminals, sensors, and power/data components.
+- **Yazaki North America** offers mobility solutions including ADAS (Advanced Driver Assistance Systems), powertrain, and electronics.
+- **ZF Gainesville LLC** supplies thermal systems, electrification, ADAS (Advanced Driving Assistance System) components, and powertrain parts.
+- **Yamaha Motor Manufacturing Corp.** provides automotive electrical architecture, connectivity, and advanced safety components.</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -796,7 +794,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -807,7 +805,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -835,15 +833,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Based on the provided context about Georgia EV supply chain companies, there are no explicit vehicle assembly entities listed. The companies mentioned are primarily involved in manufacturing parts and components rather than assembling vehicles. However, if we consider those with significant employment numbers as potentially key players in a broader assembly or major component production role:
-1. **Vernay** - Employment: 1600 | Primary OEMs: Hyundai/Kia
-2. **Toyota Industries Group (TACG-TICA)** - Employment: 18,100 | Primary OEMs: Freightliner/Western Star
-3. **TN Americas Holding Inc.** - Employment: 19,600 | Primary OEMs: Volvo/Mack, buses, construction equipment
-These companies have substantial employment numbers and are linked to major OEMs, indicating they play significant roles in the supply chain that could include assembly or large-scale component manufacturing for electric vehicles.</t>
+          <t>Based on the provided context about Georgia EV supply chain companies, there are no explicit vehicle assembly entities listed. All entries pertain to manufacturing plants that produce components or parts for vehicles rather than assembling complete vehicles. However, some companies have significant employment numbers and serve as OEM parent groups:
+- **Toyota Industries Group (TACG-TICA)**: Primary Facility Type is Corporate Operations with 18,100 employees.
+- **TN Americas Holding Inc.**: Also a corporate operations entity with 19,600 employees.
+These entities are involved in commercial vehicles and powertrains but do not directly engage in vehicle assembly as per the given information.</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3.88</v>
+        <v>2.86</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -865,7 +862,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -894,29 +891,29 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Here are the companies in Georgia with "EV / Battery Relevant" set to Yes along with their EV Supply Chain Role and Category:
+          <t>Here are the companies with "EV / Battery Relevant" set to Yes along with their EV Supply Chain Role and Category:
 1. **Hitachi Astemo Americas Inc.**
-   - EV Supply Chain Role: Battery Cell
-   - Category: Tier 1/2
-2. **ZF Gainesville LLC** (Multiple Entries)
-   - EV Supply Chain Role: EV thermal management and power electronics, EV thermal systems and electronics, EV body, powertrain, and thermal components
-   - Category: OEM Supply Chain
+   - **Category:** Tier 1/2
+   - **EV Supply Chain Role:** Battery Cell
+2. **ZF Gainesville LLC (multiple entries)**
+   - **Category:** OEM Supply Chain, OEM Footprint
+   - **EV Supply Chain Role:** EV thermal management and power electronics, EV body, powertrain, and thermal components, EV thermal systems and electronics
 3. **Woodbridge Foam Corp.**
-   - EV Supply Chain Role: EV wiring harnesses and power distribution
-   - Category: OEM Supply Chain
+   - **Category:** OEM Supply Chain
+   - **EV Supply Chain Role:** EV wiring harnesses and power distribution
 4. **Yamaha Motor Manufacturing Corp.**
-   - EV Supply Chain Role: Advanced electrical architecture for EVs
-   - Category: OEM Supply Chain
+   - **Category:** OEM Supply Chain
+   - **EV Supply Chain Role:** Advanced electrical architecture for EVs
 5. **Woory Industrial Co.**
-   - EV Supply Chain Role: High-voltage EV connectors and electronics
-   - Category: OEM Supply Chain
+   - **Category:** OEM Supply Chain
+   - **EV Supply Chain Role:** High-voltage EV connectors and electronics
 6. **Yazaki North America**
-   - EV Supply Chain Role: Power electronics, sensors, and EV systems
-   - Category: OEM Footprint</t>
+   - **Category:** OEM Footprint
+   - **EV Supply Chain Role:** Power electronics, sensors, and EV systems</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4.68</v>
+        <v>4.94</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -927,7 +924,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
@@ -938,7 +935,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -976,7 +973,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -987,7 +984,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1027,11 +1024,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The Industry Group "Electronic and Other Electrical Equipment and Components" is represented among Battery Cell companies in Georgia EV supply chain. This can be seen with Hitachi Astemo Americas Inc., which manufactures battery cells for electric mobility. No other companies listed specifically fall under the category of Battery Pack, so this is the only relevant industry group provided based on the context given.</t>
+          <t>Among the provided context, only one company is directly involved in Battery Cell production:
+- **Hitachi Astemo Americas Inc.** (Industry Group: Electronic and Other Electrical Equipment and Components)
+No companies are listed as specifically producing Battery Packs. Therefore, the set of Industry Groups represented among Battery Pack and Battery Cell companies based on the given information includes:
+- Electronic and Other Electrical Equipment and Components</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
@@ -1082,18 +1082,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Based on the provided context:
-- **Tier 1**: 0 companies listed under this category.
-- **Tier 2/3**: 0 companies listed under this category.
-- **Tier 1/2**: 0 companies listed under this category.
-- **OEM (Footprint)**: 3 companies (Toyota Industries Group (TACG-TICA), Trenton Pressing, TN Americas Holding Inc.).
-- **OEM Supply Chain**: 4 companies (Valeo, Vista Metals Corp., Wabash National Corp., Volvo Group North America).
-- **OEM Footprint** (Note: This is a duplicate of OEM (Footprint) in the context): 3 companies (Toyota Industries Group (TACG-TICA), Trenton Pressing, TN Americas Holding Inc.).
-The dataset does not include any companies under Tier 1 or Tier 2/3 categories.</t>
+          <t>Based on the provided context about Georgia EV supply chain companies:
+- **Tier 1/2**: None listed.
+- **Tier 1**: Valeo (listed under Tier 1 automotive components).
+- **OEM**: None specifically listed as OEM only, but Toyota Industries Group and TN Americas Holding Inc. are listed under OEM parent group footprint.
+- **OEM Supply Chain**: Vista Metals Corp., Wabash National Corp., Volvo Group North America.
+- **OEM (Footprint)**: Toyota Industries Group (TACG-TICA), Trenton Pressing, TN Americas Holding Inc.
+- **Tier 2/3**: None listed.
+Therefore:
+- Tier 1: 1 company
+- OEM Supply Chain: 3 companies
+- OEM (Footprint): 3 companies
+Note: The context does not provide distinct entries for "Tier 2/3" and "OEM Footprint," but the information given allows us to categorize companies accordingly.</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3.78</v>
+        <v>4.06</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -1104,7 +1108,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
@@ -1115,7 +1119,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="N11" t="b">
         <v>0</v>
@@ -1144,7 +1148,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Here are the companies located in Troup County along with their category, EV supply chain role, and employment:
+          <t>Here are the companies located in Troup County along with their respective categories, EV supply chain roles, and employment:
 1. **PPG Industries Inc.**
    - Category: Tier 1
    - EV Supply Chain Role: General Automotive
@@ -1168,7 +1172,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>4.04</v>
+        <v>4.07</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -1179,7 +1183,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
@@ -1190,7 +1194,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="N12" t="b">
         <v>0</v>
@@ -1221,14 +1225,13 @@
         <is>
           <t>Based on the provided context, only one company is categorized as a Tier 1 supplier:
 - **Linde + Wiemann** in Troup County
-Since there are no other Tier 1 suppliers listed from other counties, Troup County has the highest number of Tier 1 suppliers with 1. Therefore, the top 5 counties by the count of Tier 1 suppliers would simply be:
-1. Troup County: 1
-2. No other county is listed with a Tier 1 supplier.
-Thus, only Troup County meets the criteria for having any Tier 1 suppliers in Georgia's EV supply chain context provided here.</t>
+Since there are no other Tier 1 suppliers listed from other counties, Troup County has the highest number of Tier 1 suppliers with 1.
+Top 5 Counties (only relevant county included due to lack of additional Tier 1 suppliers):
+1. Troup County: 1</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2.74</v>
+        <v>2.06</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -1250,7 +1253,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="N13" t="b">
         <v>0</v>
@@ -1290,15 +1293,15 @@
    - Industry Group: Transportation Equipment
    - Product/Service: Engine components, turbochargers, exhaust parts and other automotive parts
 4. **Michelin Tread Technologies**
-   - Industry Group: Not specified (Automotive accessories)
+   - Industry Group: Not specified (implied to be related to Automotive Accessories)
    - Product/Service: Ventvisors, hood shields, floor mats, automotive accessories
 5. **MAT Heavy Duty**
-   - Industry Group: Not specified (Vehicle protection and interior comfort products)
+   - Industry Group: Not specified (implied to be related to Vehicle Protection and Interior Comfort Products)
    - Product/Service: Vehicle protection and interior comfort products</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3.79</v>
+        <v>3.98</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -1309,7 +1312,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
@@ -1353,7 +1356,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -1364,7 +1367,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -1406,17 +1409,17 @@
         <is>
           <t>The city that has both Tier 1 and Tier 2/3 companies present is Troup County. 
 - **Tier 1 Company:** Linde + Wiemann (6-speed automatic transmissions)
-- **Tier 2/3 Companies:** No other Tier 2/3 company listed in Troup County, but it hosts the only Tier 1 company mentioned.
-However, if we consider cities with multiple companies regardless of their tier classification strictly from the given data:
+- **Tier 2/3 Companies:** No other Tier 2/3 company listed in Troup County.
+However, if we consider the presence of both tiers within a city more broadly across the provided data:
 **Statesboro, Bulloch County:**
 - Tier 2/3 Company: Ascend Elements (Interior and exterior plastic parts)
 **Albany, Dougherty County:**
-- Tier 2/3 Companies: First American Resources (Honeycomb material) 
-Since Statesboro and Albany have multiple companies but only one is Tier 2/3 with no Tier 1 company listed in the context provided, Troup County remains the sole location meeting the criteria of having both tiers if we strictly adhere to the question's requirement.</t>
+- Tier 2/3 Companies: First American Resources (Honeycomb material)
+There is no city that has both a Tier 1 and Tier 2/3 company present based on the provided context.</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>4.02</v>
+        <v>3.31</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -1467,12 +1470,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>The only company involved in Battery Pack production mentioned in the context is Hyundai Motor Group, located in McDonough, Henry County. Therefore:
+          <t>The only company involved in the Battery Pack role is Hyundai Motor Group, located in McDonough, Henry County. Therefore:
 - **Henry County**: Hyundai Motor Group</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -1483,7 +1486,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
@@ -1527,7 +1530,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -1538,18 +1541,18 @@
         </is>
       </c>
       <c r="J18" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
         <v>0.1</v>
-      </c>
-      <c r="K18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="M18" t="n">
-        <v>0.11</v>
       </c>
       <c r="N18" t="b">
         <v>0</v>
@@ -1578,11 +1581,13 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>For companies located in Fulton County with an EV Supply Chain Role of "General Automotive," the total employment is 400. This includes Elan Technology Inc. (160 employees), SRG Global Inc. (60 employees), and Sewon America Inc. (80 employees). TI Fluid Systems has a different role ("OEM corporate footprint influencing EV strategy") and employs 19,600 people, which is not included in the total for "General Automotive" role.</t>
+          <t>The total employment by EV Supply Chain Role for companies located in Fulton County is as follows:
+- **General Automotive**: 400 (Elan Technology Inc. with 160 employees + SRG Global Inc. with 60 employees + Sewon America Inc. with 80 employees)
+Note: TI Fluid Systems has an EV/Battery relevant role but its employment figure of 19,600 is for the North American Headquarters and not specifically tied to Fulton County's EV supply chain activities as per the provided context.</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -1593,7 +1598,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="K19" t="b">
         <v>0</v>
@@ -1633,7 +1638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>The companies located in Georgia with their respective categories and EV supply chain roles are:
+          <t>The companies located in Georgia with specified categories and EV supply chain roles are:
 1. **ADVICS Manufacturing Georgia LLC**
    - **Category:** Tier 2/3
    - **EV Supply Chain Role:** General Automotive
@@ -1677,7 +1682,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="N20" t="b">
         <v>0</v>
@@ -1705,14 +1710,15 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>For companies with "EV / Battery Relevant" marked as "Yes," the distribution by county in Georgia is as follows:
+          <t>For companies with "EV / Battery Relevant" set to "Yes," the distribution by county is as follows:
 - **Bryan County**: Honda Development &amp; Manufacturing (400 employees)
 - **Hart County**: SK Battery America (75 employees)
-- **Coweta County**: Hitachi Astemo Americas Inc. (723 employees)</t>
+- **Coweta County**: Hitachi Astemo Americas Inc. (723 employees)
+These companies are directly involved in EV battery production or related components and have manufacturing plants located in the specified counties of Georgia.</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -1762,11 +1768,11 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Based on the provided context about Georgia EV supply chain companies, there are no companies listed with a Primary Facility Type of "Headquarters" or "North American Headquarters." All entries specify different types of manufacturing plants or regional corporate operations. Therefore, no companies meet the criteria specified in the question.</t>
+          <t>Based on the provided context, there are no companies listed with a Primary Facility Type of "Headquarters" in Georgia's EV supply chain. All entries specify different types of manufacturing plants or regional corporate operations. Therefore, the answer to your query is that there are no such companies meeting the specified criteria.</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -1777,7 +1783,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
@@ -1788,7 +1794,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="N22" t="b">
         <v>0</v>
@@ -1816,13 +1822,14 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Based on the provided context about Georgia EV supply chain companies:
+          <t>Based on the provided context:
 - **Trenton Pressing** has its primary facility type as Regional corporate operations in Georgia with 350 employees.
-- **Toyota Industries Group (TACG-TICA)** operates a Corporate operations facility in Georgia, employing 18,100 people.</t>
+- **Toyota Industries Group (TACG-TICA)** operates with Corporate operations in Georgia and employs 18,100 people.
+These companies are cited within the EV supply chain context for their significant roles and locations.</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -1833,7 +1840,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="K23" t="b">
         <v>0</v>
@@ -1873,11 +1880,11 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>None of the provided companies in the context have a Primary Facility Type listed as R&amp;D. The closest related to research and development activities is ZF Gainesville LLC, which has one entry with "Primary Facility Type: Engineering / Operations," but this does not match the specific type requested (R&amp;D).</t>
+          <t>None of the provided companies in the context have a Primary Facility Type listed as R&amp;D. The closest related company is ZF Gainesville LLC, which has one entry listing its Primary Facility Type as Engineering / Operations, but this does not match the specified "R&amp;D" type exactly. Therefore, there are no companies that fit the criteria of having a Primary Facility Type = R&amp;D in the given context.</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -1899,7 +1906,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
@@ -1928,34 +1935,34 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>### Automotive Textiles and Interiors
+          <t>### Automotive Textiles and Interiors:
 - **Wheelabrator Group Inc.**
   - Primary Facility Type: Manufacturing plant
   - Product / Service: Metal stamping &amp; fabrication for automotive/industrial components
-### Automotive Plastic Components
+### Automotive Plastic Components:
 - **Wabash National Corp.**
   - Primary Facility Type: Manufacturing plant
   - Product / Service: Automotive parts contract manufacturing (assemblies/components)
-### Automotive Modules and Components
+### Automotive Modules and Components:
 - **Vista Metals Corp.**
   - Primary Facility Type: Manufacturing plant
   - Product / Service: Automotive modules/powertrain components; parts supply
-### Primary Metal Industries
+### Primary Metal Industries:
 - **Ecoplastic Corporation**
   - Primary Facility Type: Manufacturing Plant
   - Product / Service: Flexible shafts for automotive transmissions
-### Automotive Parts Manufacturing
+### Automotive Parts Manufacturing:
 - **Valeo**
   - Primary Facility Type: Manufacturing plant
   - Product / Service: Automotive body/stamped metal assemblies (Kia/Hyundai supply chain)
-### Automotive Stamping and Assemblies
+### Automotive Stamping and Assemblies:
 - **Vernay**
   - Primary Facility Type: Manufacturing plant
   - Product / Service: Automotive metal stamping &amp; body parts manufacturing (Hyundai/Kia supplier)</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -2006,12 +2013,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Among companies with Primary Facility Type containing 'Corporate operations' that are also EV/Battery Relevant = Yes, the company is:
+          <t>Among companies with Primary Facility Type containing 'Corporate operations' that are also EV / Battery Relevant = Yes, the relevant company is:
 - TN Americas Holding Inc.</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -2022,7 +2029,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="K26" t="b">
         <v>0</v>
@@ -2062,11 +2069,11 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Based on the provided context, there are no companies listed that have a Primary Facility Type containing both Engineering and Manufacturing. All companies listed either have a facility type of "Manufacturing Plant" or "Regional corporate operations," but none combine Engineering with Manufacturing in their description. Therefore, there are no relevant Product / Service details to list for this criteria.</t>
+          <t>Based on the provided context, there are no companies listed that have a Primary Facility Type containing both Engineering and Manufacturing. Therefore, I cannot provide any products or services for such companies as they do not exist in the given data.</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1.81</v>
+        <v>1.38</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -2077,7 +2084,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="K27" t="b">
         <v>0</v>
@@ -2117,26 +2124,34 @@
       <c r="F28" t="inlineStr">
         <is>
           <t>To calculate the average employment for each primary facility type based on the provided context:
-1. **Regional Corporate Operations**:
+1. **Regional Corporate Operations**
    - Trenton Pressing (Employment: 350)
    - Toyota Industries Group (TACG-TICA) (Employment: 18100)
    - TN Americas Holding Inc. (Employment: 19600)
-   Average Employment = \(\frac{350 + 18100 + 19600}{3} = \frac{37950}{3} = 12650\)
-2. **Manufacturing Plant**:
+   Average Employment:
+   \[
+   \frac{350 + 18100 + 19600}{3} = \frac{37050}{3} = 12350
+   \]
+2. **Manufacturing Plant**
    - Wabash National Corp. (Employment: 20)
    - Ecoplastic Corporation (Employment: 160)
    - Linde + Wiemann (Employment: 515)
    - PPG Industries Inc. (Employment: 120)
-   Average Employment = \(\frac{20 + 160 + 515 + 120}{4} = \frac{815}{4} = 203.75\)
-3. **Manufacturing / OEM Operations**:
+   Average Employment:
+   \[
+   \frac{20 + 160 + 515 + 120}{4} = \frac{815}{4} = 203.75
+   \]
+3. **Manufacturing / OEM Operations**
    - TI Fluid Systems (Employment: 80)
-   Average Employment = \(80\) (only one company in this category)
-Summary of Averages:
-- Regional Corporate Operations: 12</t>
+   Average Employment:
+   \[
+   80
+   \]
+Summary of average employment by primary facility</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>5.89</v>
+        <v>5.9</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -2186,13 +2201,13 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Based on the provided context, there is only one company listed as a Tier 1 supplier:
-- **PPG Industries Inc.** | Category: Tier 1 | Employment: 120
-Since this is the sole Tier 1 supplier mentioned in the sources and no other Tier 1 suppliers are listed, PPG Industries Inc. has the highest (and only) average employment among Tier 1 suppliers with 120 employees.</t>
+          <t>Based on the provided context, there is only one Tier 1 supplier listed:
+- **PPG Industries Inc.** with an EV Supply Chain Role of "General Automotive" and Employment of 120.
+Since this is the sole Tier 1 supplier mentioned in the context, it automatically has the highest average employment among Tier 1 suppliers with 120 employees.</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -2203,7 +2218,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -2243,11 +2258,11 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>There are no Tier 2/3 suppliers listed in the provided context that have employment of 500 or more. All Tier 2/3 companies mentioned have fewer than 500 employees.</t>
+          <t>Based on the provided context, there are no Tier 2/3 suppliers in Georgia's EV supply chain that have employment of 500 or more. All listed Tier 2/3 companies have fewer than 500 employees.</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -2269,7 +2284,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="N30" t="b">
         <v>0</v>
@@ -2297,14 +2312,14 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>The Tier 1/2 companies with EV/Battery Relevant set to "Yes" and their primary OEMs are:
+          <t>The Tier 1/2 companies in Georgia that are relevant to the EV/battery supply chain and have specified primary Original Equipment Manufacturers (OEMs) are:
 - **Hitachi Astemo Americas Inc.**
   - Primary OEMs: Hyundai Kia
-These companies play significant roles in the electric vehicle supply chain according to the provided context.</t>
+No other Tier 1/2 company listed meets both criteria of having "EV / Battery Relevant" set to Yes and specifying primary OEMs.</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1.64</v>
+        <v>2.01</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -2315,7 +2330,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
@@ -2326,7 +2341,7 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="N31" t="b">
         <v>0</v>
@@ -2355,18 +2370,21 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Among the provided Georgia EV supply chain companies:
-- **EV / Battery Relevant = Yes**: None of the listed materials companies have an "EV / Battery Relevant" status marked as Yes.
+          <t>Among the listed Georgia EV supply chain companies:
+- **EV / Battery Relevant = Yes**: None of the provided sources list any materials companies as being directly relevant to EV or battery production.
 - **Indirect**: 
   - Global Powertrain Systems LLC (Fabricates metal products, including coated coils, metal wall and roof systems and aluminum recreational vehicle doors)
   - FREYR Battery (Decorative and functional coating systems)
 Counts:
-- EV / Battery Relevant = Yes: 0
-- Indirect: 2</t>
+- Directly Relevant: 0
+- Indirect: 2
+Lists:
+- Directly Relevant: None
+- Indirect: Global Powertrain Systems LLC, FREYR Battery</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2.47</v>
+        <v>2.83</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -2388,7 +2406,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="N32" t="b">
         <v>0</v>
@@ -2417,22 +2435,24 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>The context provided lists five distinct industry groups for Georgia EV supply chain companies:
-1. Commercial vehicles and powertrains (Toyota Industries Group)
-2. Automotive textiles and interiors (Wheelabrator Group Inc.)
-3. Automotive precision components (Trenton Pressing Inc.)
-4. Electrical connectors and sensors (Woory Industrial Co.)
-5. Automotive modules and components (Vista Metals Corp.)
-The largest industry group by count in the dataset is "Commercial vehicles and powertrains," with one company listed: Toyota Industries Group.
+          <t>The provided context includes companies from different Industry Groups. To determine which Industry Group has the largest number of companies and to list the top 3 Industry Groups by count:
+1. **Commercial vehicles and powertrains**: This group is represented by Toyota Industries Group (TACG-TICA) only.
+2. **Automotive textiles and interiors**: Represented by Wheelabrator Group Inc.
+3. **Automotive precision components**: Represented by Trenton Pressing Inc.
+4. **Electrical connectors and sensors**: Represented by Woory Industrial Co.
+5. **Automotive modules and components**: Represented by Vista Metals Corp.
+6. **Primary Metal Industries**: Represented by Dongwon Autopart Technology Georgia LLC (though it is not EV/Battery relevant).
+7. **Metal stamping and assemblies**: Represented by Volvo Group North America.
 The top 3 Industry Groups by count are:
-1. Commercial vehicles and powertrains
-2. Automotive textiles and interiors
-3. Automotive precision components
-Each of these groups has only one company listed in the provided context, making them tied for having the largest number within this limited dataset.</t>
+1. **Electrical connectors and sensors** with one company: Woory Industrial Co.
+2. Each of the following groups has only one company as well, but listing three:
+   - **Automotive textiles and interiors**: Wheelabrator Group Inc.
+   - **Automotive precision components**: Trenton Pressing Inc.
+Since each Industry Group mentioned above contains just a single company in this dataset, there is no clear largest group by count. All listed groups have an equal number of companies (one per group).</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>3.47</v>
+        <v>5.64</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -2454,7 +2474,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="N33" t="b">
         <v>0</v>
@@ -2486,11 +2506,11 @@
           <t>Within the Industry Group 'Electrical connectors and sensors' (which falls under the broader category of Electronic and Other Electrical Equipment and Components), there is one company listed:
 - **Woory Industrial Co.**
   - EV Supply Chain Role: High-voltage EV connectors and electronics
-There are no companies explicitly listed in an industry group called 'Electronic and Other Electrical Equipment and Components' as per the provided context, but Woory Industrial Co. operates within a closely related field of electrical connectors and sensors.</t>
+Additionally, within the context provided, Woodbridge Foam Corp. and ZF Gainesville LLC do not fall directly into the 'Electrical connectors and sensors' industry group but are relevant to automotive electrical systems and components. However, since the question specifically asks for companies in the 'Electronic and Other Electrical Equipment and Components' industry group, only Woory Industrial Co. fits this criterion based on the given context.</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2.26</v>
+        <v>2.94</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -2501,7 +2521,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
@@ -2512,7 +2532,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="N34" t="b">
         <v>0</v>
@@ -2541,11 +2561,11 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Within the category of "Rubber and Miscellaneous Plastic Products," there is no company listed as EV/Battery Relevant = Yes. However, it's important to note that Woodbridge Foam Corp., which falls under the OEM Supply Chain rather than Rubber and Miscellaneous Plastic Products, is EV/Battery Relevant = Yes.</t>
+          <t>Within the category of "Rubber and Miscellaneous Plastic Products," there is no company listed as EV/Battery Relevant = Yes. However, Woodbridge Foam Corp., which falls under the "Automotive electrical systems" Industry Group, is noted to be EV/Battery Relevant = Yes with its role in manufacturing EV wiring harnesses and power distribution systems.</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -2556,7 +2576,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
@@ -2596,11 +2616,11 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Based on the provided context about Georgia EV supply chain companies, there are no companies listed with an EV Supply Chain Role described as "General Automotive" where EV/Battery Relevant is marked as Yes. The roles mentioned in the sources include specific functions such as wiring harnesses, thermal management, power electronics, and electrical architecture rather than a general automotive role. Therefore, no matches were found for the criteria specified in the question.</t>
+          <t>Based on the provided context about Georgia EV supply chain companies, there are no companies listed with an EV Supply Chain Role described as "General Automotive" where EV/Battery Relevant is marked as Yes. The roles mentioned in the sources include specific functions such as wiring harnesses, thermal management, power electronics, and body/chassis components for both EVs and ICE vehicles, but none fit the exact criteria of having a role labeled as "General Automotive."</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -2622,7 +2642,7 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="N36" t="b">
         <v>0</v>
@@ -2651,11 +2671,11 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>None of the provided companies are listed as being in the Charging Infrastructure role. The companies mentioned—Woodbridge Foam Corp., Woory Industrial Co., Hitachi Astemo Americas Inc., TN Americas Holding Inc., and Toyota Industries Group (TACG-TICA)—are involved in other roles within the EV supply chain such as wiring harnesses, connectors, battery cells, OEM footprints for electric vehicles, and commercial vehicle manufacturing.</t>
+          <t>None of the provided companies are listed as being in the Charging Infrastructure role. The companies mentioned (Woodbridge Foam Corp., Woory Industrial Co., Hitachi Astemo Americas Inc., TN Americas Holding Inc., and Toyota Industries Group) are involved in roles such as EV wiring harnesses, high-voltage connectors, battery cells, OEM parent group footprints, but not charging infrastructure.</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -2706,7 +2726,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Here are the companies linked to Hyundai Kia along with their category, EV supply chain role, and location:
+          <t>Here are the companies linked to Hyundai Kia with their respective categories, EV Supply Chain Roles, and locations:
 1. **Hyundai Industrial Co.**
    - **Category:** Tier 1/2
    - **EV Supply Chain Role:** General Automotive
@@ -2714,7 +2734,7 @@
 2. **Vernay**
    - **Category:** OEM Supply Chain
    - **EV Supply Chain Role:** Stamped and welded assemblies for OEMs
-   - **Location:** Georgia (specific city not provided)
+   - **Location:** Georgia (specific county not provided)
 3. **Hitachi Astemo Americas Inc.**
    - **Category:** Tier 1/2
    - **EV Supply Chain Role:** Battery Cell
@@ -2722,11 +2742,11 @@
 4. **Valeo**
    - **Category:** OEM Supply Chain
    - **EV Supply Chain Role:** Tier 1 automotive components
-   - **Location:** Georgia (specific city not provided)</t>
+   - **Location:** Georgia (specific county not provided)</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -2748,7 +2768,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="N38" t="b">
         <v>0</v>
@@ -2777,7 +2797,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>The companies linked to Hyundai Motor Group and their respective products/services are:
+          <t>The companies linked to Hyundai Motor Group and their products/services include:
 1. **Hyundai Industrial Co.**
    - Location: Valdosta, Lowndes County
    - Product/Service: Automotive batteries
@@ -2786,17 +2806,17 @@
    - Product/Service: Storage batteries
 3. **Hyundai Transys Georgia Seating Systems**
    - Location: Marietta, Cobb County
-   - Product/Service: Automotive electronics, resonators, capacitors, resistors, electronics and electronic parts
+   - Product/Service: Automotive electronics, resonators, capacitors, resistors, and electronic parts
 4. **Vernay**
    - Location: Georgia (specific city not provided)
-   - Product/Service: Automotive metal stamping &amp; body parts manufacturing (Hyundai/Kia supplier)
+   - Product/Service: Automotive metal stamping &amp; body parts manufacturing
 5. **Enchem America Inc.**
    - Location: Cumming, Forsyth County
    - Product/Service: Electric wiring components</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>3.86</v>
+        <v>3.73</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -2818,7 +2838,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="N39" t="b">
         <v>0</v>
@@ -2847,16 +2867,16 @@
       <c r="F40" t="inlineStr">
         <is>
           <t>The suppliers linked to Rivian Automotive are:
-1. **Rivian Automotive**  
-   - Employment: 105  
+1. **Rivian Automotive**
+   - Employment: 105
    - Location: Gainesville, Hall County
-2. **Racemark International LLC**  
-   - Employment: 120  
+2. **Racemark International LLC**
+   - Employment: 120
    - Location: Calhoun, Gordon County</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -2907,13 +2927,13 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>The only entry with "Primary OEMs: Multiple OEMs" is Adient. Since there is only one entry, the median Employment value is 180. 
+          <t>The only entry with "Primary OEMs: Multiple OEMs" is Adient. Since there is only one entry meeting this criterion, the median Employment value is 180. 
 Company: Adient  
 Employment: 180</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -2924,7 +2944,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>0.19</v>
+        <v>0.12</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -2935,7 +2955,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="N41" t="b">
         <v>0</v>
@@ -2964,11 +2984,11 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Based on the provided context, there are no direct links specified between Mercedes-Benz USA LLC and any other company. However, Mercedes-Benz USA LLC has an "EV / Battery Relevant" status of "Indirect," indicating it is involved in the EV supply chain but not directly related to battery manufacturing or cell production.</t>
+          <t>Based on the provided context, there are no direct links specified between Mercedes-Benz USA LLC and other companies. However, Mercedes-Benz USA LLC is listed as having an "EV / Battery Relevant" status of "Indirect". No other company in the list is explicitly linked to Mercedes-Benz USA LLC for EV supply chain purposes.</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -3019,14 +3039,15 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>The company linked to SK Battery America based on the provided context is not explicitly connected to another company through affiliation or supplier relationships. However, SK Battery America's own details are:
+          <t>The context provided does not list any direct company linked to SK Battery America. However, it provides information about SK Battery America itself. According to the sources:
+- **Company:** SK Battery America
 - **EV Supply Chain Role:** Materials
 - **Location:** Hartwell, Hart County
-Since no other companies are directly cited as being affiliated with SK Battery America in the given sources, this information pertains solely to SK Battery America itself.</t>
+There is no mention of another company directly linked to SK Battery America in the given context.</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -3037,18 +3058,18 @@
         </is>
       </c>
       <c r="J43" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
         <v>0.1</v>
-      </c>
-      <c r="K43" t="b">
-        <v>0</v>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="M43" t="n">
-        <v>0.11</v>
       </c>
       <c r="N43" t="b">
         <v>0</v>
@@ -3077,11 +3098,27 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Based on the provided context, there are no direct links or associations mentioned between any of the listed companies (Woodbridge Foam Corp., Vista Metals Corp., ZF Gainesville LLC, Yamaha Motor Manufacturing Corp.) and Club Car LLC. Therefore, I cannot provide a list of companies linked to Club Car LLC with their EV Supply Chain Role and Product / Service as per your request.</t>
+          <t>Based on the provided context about Georgia EV supply chain companies, there is no direct mention of any company being linked to Club Car LLC. The listed companies are:
+1. **Woodbridge Foam Corp.**
+   - **EV Supply Chain Role:** EV wiring harnesses and power distribution
+   - **Product / Service:** Automotive wiring harnesses &amp; electrical distribution systems
+2. **Vista Metals Corp.**
+   - **EV Supply Chain Role:** EV and ICE component manufacturing
+   - **Product / Service:** Automotive modules/powertrain components; parts supply
+3. **ZF Gainesville LLC**
+   - **EV Supply Chain Role:** EV body, powertrain, and thermal components (Source 5)
+   - **Product / Service:** Contract manufacturing &amp; automotive systems (body, chassis, powertrain, e-drive)
+4. **ZF Gainesville LLC** 
+   - **EV Supply Chain Role:** EV thermal management and power electronics
+   - **Product / Service:** Automotive supplier footprint (electrification, thermal, powertrain, ADAS components)
+5. **Yamaha Motor Manufacturing Corp.**
+   - **EV Supply Chain Role:** Advanced electrical architecture for EVs
+   - **Product / Service:** Automotive electrical architecture, connectivity, and advanced safety components
+None of these companies are explicitly linked to Club Car LLC in the given context.</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1.81</v>
+        <v>5.29</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -3103,7 +3140,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="N44" t="b">
         <v>0</v>
@@ -3134,12 +3171,13 @@
         <is>
           <t>The companies linked to Blue Bird Corp. and their primary facility types are:
 1. **TE Connectivity** - Primary Facility Type: Manufacturing Plant (Located in Fort Valley, Peach County)
-2. **Hanon Systems USA LLC** - Primary Facility Type not specified (Located in Griffin, Spalding County)
-3. **Perkins Small Engines LLC** - Primary Facility Type not specified (Located in Zebulon, Pike County)</t>
+2. **Hanon Systems USA LLC** - Primary Facility Type not specified directly but implied as a manufacturing or assembly type based on its role.
+3. **Perkins Small Engines LLC** - Primary Facility Type not specified directly but implied as a manufacturing type based on its role.
+Note: Blue Bird Corp.'s own primary facility type is listed as Manufacturing Plant in Elberton, Elbert County.</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>2.05</v>
+        <v>2.61</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -3150,18 +3188,18 @@
         </is>
       </c>
       <c r="J45" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
         <v>0.1</v>
-      </c>
-      <c r="K45" t="b">
-        <v>0</v>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="M45" t="n">
-        <v>0.09</v>
       </c>
       <c r="N45" t="b">
         <v>0</v>
@@ -3190,7 +3228,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Based on the provided context, the companies linked to Yamaha Motor Manufacturing Corp., including their category, location, and employment details are:
+          <t>Based on the provided context:
 1. **Teklas USA**
    - **Category:** OEM
    - **Location:** Coweta County, Georgia
@@ -3199,14 +3237,14 @@
    - **Category:** OEM Supply Chain
    - **Location:** Georgia
    - **Employment:** 298
-3. **Trenton Pressing (Footprint)**
-   - **Category:** OEM (Footprint)
+3. **Yamaha Motor Manufacturing Corp.**
+   - **Category:** OEM Supply Chain
    - **Location:** Georgia
-   - **Employment:** 350</t>
+   - **Employment:** 190,000</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>3.05</v>
+        <v>2.66</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -3228,7 +3266,7 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="N46" t="b">
         <v>0</v>
@@ -3260,11 +3298,11 @@
           <t>Based on the provided context:
 - **TN Americas Holding Inc.**: 2 companies (Source 2 and Source 7)
 - **Toyota Industries Group (TACG-TICA)**: 1 company (Source 6)
-These are the only OEMs with associated companies listed in the given sources, excluding blanks or unspecified entries.</t>
+These are the only OEMs listed with associated companies in Georgia's EV supply chain context.</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -3275,7 +3313,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K47" t="b">
         <v>0</v>
@@ -3315,11 +3353,11 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>The primary OEM with the highest total employment across its associated companies in Georgia is TN Americas Holding Inc., with 19,600 employees. This company is involved in commercial vehicles and powertrains and acts as an OEM parent group footprint for EV and HD electrification.</t>
+          <t>TN Americas Holding Inc. has the highest total employment among the provided companies with 19,600 employees at its Georgia facility. While Woory Industrial Co. reports an employment figure of 87,000, it is not clear if this company is directly associated with an OEM in the same manner as TN Americas Holding Inc., based on the given context.</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -3330,7 +3368,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
@@ -3370,14 +3408,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Based on the provided context, the companies that supply to more than one OEM are:
-1. **NIFCO KTW America Corp.** - Primary OEMs: Multiple OEMs
-2. **Hyundai Industrial Co.** - Primary OEMs: Multiple OEMs
-These companies indicate they serve multiple Original Equipment Manufacturers (OEMs) in the automotive industry.</t>
+          <t>Based on the provided context and focusing on the "Primary OEMs" field, the following companies supply to more than one OEM:
+1. **NIFCO KTW America Corp.**
+   - Primary OEMs: Multiple OEMs
+2. **Hyundai Industrial Co.**
+   - Primary OEMs: Multiple OEMs
+These companies are indicated as supplying to multiple Original Equipment Manufacturers (OEMs).</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -3428,7 +3468,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Based on the provided context, among the companies linked to Hyundai and Kia, the following are listed:
+          <t>Among the companies listed in the context that are linked to Hyundai or Kia, and considering their roles within the EV supply chain:
 1. **Vernay**
    - **EV Supply Chain Role:** Stamped and welded assemblies for OEMs
    - **Product / Service:** Automotive metal stamping &amp; body parts manufacturing (Hyundai/Kia supplier)
@@ -3438,7 +3478,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -3449,7 +3489,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>0.22</v>
+        <v>0.09</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
@@ -3460,7 +3500,7 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="N50" t="b">
         <v>0</v>
@@ -3491,15 +3531,16 @@
         <is>
           <t>The companies linked to Porsche Cars North America Inc. are:
 1. **Minebea AccessSolutions USA Inc.**
-   - Location: Atlanta, Fulton County
-   - Employment: Not specified
-2. **Porsche Cars North America Inc. (itself)**
-   - Location: Cairo, Grady County
-   - Employment: 125</t>
+   - **Location:** Atlanta, Fulton County
+   - **Employment:** Not specified
+2. **Porsche Cars North America Inc.** (itself)
+   - **Location:** Cairo, Grady County
+   - **Employment:** 125
+These are the companies directly associated with Porsche Cars North America Inc. based on the provided context.</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -3510,7 +3551,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -3552,13 +3593,13 @@
         <is>
           <t>The OEM-linked entries missing the "Supplier or Affiliation Type" field are:
 1. **Vista Metals Corp.** - Category: OEM Supply Chain
-2. **TN Americas Holding Inc. (listed twice but only one entry is OEM footprint)** - Category: OEM (Footprint)
+2. **TN Americas Holding Inc.** (listed twice but only one entry is OEM linked) - Category: OEM (Footprint)
 3. **Yamaha Motor Manufacturing Corp.** - Category: OEM Supply Chain
 These companies do not specify a Supplier or Affiliation Type in the provided context.</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -3569,18 +3610,18 @@
         </is>
       </c>
       <c r="J52" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K52" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
         <v>0.1</v>
-      </c>
-      <c r="K52" t="b">
-        <v>0</v>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="M52" t="n">
-        <v>0.09</v>
       </c>
       <c r="N52" t="b">
         <v>0</v>
@@ -3609,39 +3650,18 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Based on the provided context, the top 10 companies by employment in Georgia's EV supply chain are:
-1. **Yazaki North America**
-   - Category: OEM Footprint
-   - Location: Georgia
-   - Employment: 230,000
-2. **Toyota Industries Group (TACG-TICA)**
-   - Category: OEM (Footprint)
-   - Location: Georgia
-   - Employment: 18,100
-3. **Woory Industrial Co.**
-   - Category: OEM Supply Chain
-   - Location: Georgia
-   - Employment: 87,000
-4. **Trenton Pressing**
-   - Category: OEM (Footprint)
-   - Location: Georgia
-   - Employment: 350
-Since the context only provides employment data for five companies with significant numbers and does not list others exceeding these figures, the remaining entries would be:
-5. **Adient**
-   - Category: Tier 2/3
-   - Location: Ringgold, Catoosa County
-   - Employment: 180
-6. **Trenton Pressing** (listed again for completeness as it's one of the companies with known employment)
-   - Category: OEM (Footprint)
-   - Location: Georgia
-   - Employment: 350
-7. **Wabash National Corp.**
-   - Category: OEM Supply Chain
-  </t>
+          <t>Based on the provided context, the top 10 companies by employment in Georgia's EV supply chain are:
+1. **Yazaki North America** - Category: OEM Footprint | Location: Georgia | Employment: 230,000
+2. **Toyota Industries Group (TACG-TICA)** - Category: OEM (Footprint) | Location: Georgia | Employment: 18,100
+3. **Woory Industrial Co.** - Category: OEM Supply Chain | Location: Georgia | Employment: 87,000
+4. **Trenton Pressing** - Category: OEM (Footprint) | Location: Georgia | Employment: 350
+5. **Adient** - Category: Tier 2/3 | Location: Ringgold, Catoosa County | Employment: 180
+6. **Wabash National Corp.** - Category: OEM Supply Chain | Location: Georgia | Employment: 20
+Note that only five companies have employment figures provided in the context and meet the criteria of having at least 350 employees, as specified by Trenton Pressing's employment number being the smallest among those listed. The remaining entries do not provide sufficient employment data to be included in this top ten list based on the given information.</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>5.88</v>
+        <v>5.42</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -3652,18 +3672,18 @@
         </is>
       </c>
       <c r="J53" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K53" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
         <v>0.11</v>
-      </c>
-      <c r="K53" t="b">
-        <v>0</v>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="M53" t="n">
-        <v>0.09</v>
       </c>
       <c r="N53" t="b">
         <v>0</v>
@@ -3692,18 +3712,18 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>The two companies with the lowest employment numbers in Georgia's EV supply chain context are:
+          <t>The two companies with the lowest employment numbers from the provided context are Vanguard National Trailer Corp. and Woodbridge Foam Corp., each having fewer employees than 90,000. Their roles in the EV supply chain are as follows:
 1. **Vanguard National Trailer Corp.**
-   - **EV Supply Chain Role:** Body and chassis components for EV and ICE OEMs
-2. **Woodbridge Foam Corp.** (listed twice but with slightly different details, both have similar employment figures)
-   - **EV Supply Chain Role:** EV wiring harnesses and power distribution
-Since only two companies are listed with distinct low employment numbers, the answer focuses on these:
-- Vanguard National Trailer Corp.: Body and chassis components for EV and ICE OEMs
-- Woodbridge Foam Corp.: EV wiring harnesses and power distribution</t>
+   - Employment: 630
+   - EV Supply Chain Role: Body and chassis components for EV and ICE OEMs
+2. **Woodbridge Foam Corp.**
+   - Employment (first instance): 1657
+   - EV Supply Chain Role: EV wiring harnesses and power distribution
+Since only two companies are listed with employment numbers lower than 90,000, there aren't ten companies meeting the criteria as specified in the question.</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>2.91</v>
+        <v>3.28</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -3714,7 +3734,7 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K54" t="b">
         <v>0</v>
@@ -3725,7 +3745,7 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="N54" t="b">
         <v>0</v>
@@ -3754,11 +3774,11 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Among EV / Battery Relevant = Yes companies, Yazaki North America has the highest Employment with 230,000 employees. Its Product / Service includes automotive supplier division (mobility solutions: ADAS, powertrain, electronics).</t>
+          <t>Among the EV/Battery Relevant = Yes companies listed, Woory Industrial Co. has the highest Employment with 87,000 employees. Its Product/Service includes automotive connectors, terminals, sensors, and power/data components.</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -3815,18 +3835,18 @@
   - Toyota Industries Group (TACG-TICA): 18100
   - Hitachi Astemo Americas Inc.: 723
   - Yazaki North America: 230000
-  Total Employment for "Yes": **287423**
+  Total Employment for EV/Battery Relevant: Yes = **277423**
 - **EV/Battery Relevant: Indirect** includes Stryten Energy. The total employment is:
   - Stryten Energy: 50
-  Total Employment for "Indirect": **50**
+  Total Employment for EV/Battery Relevant: Indirect = **50**
 - **EV/Battery Relevant: No** includes FREYR Battery. The total employment is:
   - FREYR Battery: 110
-  Total Employment for "No": **110**
-In summary, the companies categorized as EV/Battery Relevant (Yes) have a significantly higher total employment compared to those classified as Indirect or No in relevance to EV batteries.</t>
+  Total Employment for EV/Battery Relevant: No = **110**
+In summary, the companies classified as "Yes" have significantly higher employment (277423) compared to those classified as "Indirect" (50) and "No" (110).</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>5.4</v>
+        <v>5.77</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -3837,7 +3857,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="K56" t="b">
         <v>0</v>
@@ -3848,7 +3868,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="N56" t="b">
         <v>0</v>
@@ -3877,22 +3897,28 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Based on the provided context about Georgia EV supply chain companies:
-1. **EV thermal management and power electronics**: ZF Gainesville LLC (Employment: 17500)
-2. **EV body, powertrain, and thermal components**: ZF Gainesville LLC (Employment: 170000)
-3. **OEM parent group footprint (electric truck strategy)**: Toyota Industries Group (TACG-TICA) (Employment: 18100)
-4. **OEM parent group footprint (EV + HD electrification)**: TN Americas Holding Inc. (Employment: 19600)
-5. **EV wiring harnesses and power distribution**: Woodbridge Foam Corp. (Employment: 1657)
-6. **Advanced electrical architecture for EVs**: Yamaha Motor Manufacturing Corp. (Employment: 190000)
-7. **General Automotive**: Adient (Employment: 180) - Indirectly relevant
-8. **EV and ICE component manufacturing**: Vista Metals Corp. (Employment: 1500)
-The top three EV Supply Chain Roles by total Employment are:
-- **Advanced electrical architecture for EVs** (Yamaha Motor Manufacturing Corp.) with a total of 190,000 employees.
-- **EV body, powertrain, and thermal components** (ZF Gainesville LLC) with a total of 1</t>
+          <t>To determine the top three EV supply chain roles by total employment based on the provided context:
+1. **EV thermal management and power electronics**: 
+   - ZF Gainesville LLC (Employment: 17500)
+2. **EV body, powertrain, and thermal components**:
+   - ZF Gainesville LLC (Employment: 170000)
+3. **Advanced electrical architecture for EVs**:
+   - Yamaha Motor Manufacturing Corp. (Employment: 190000)
+4. **OEM parent group footprint (electric truck strategy)**:
+   - Toyota Industries Group (TACG-TICA) (Employment: 18100)
+5. **OEM parent group footprint (EV + HD electrification)**:
+   - TN Americas Holding Inc. (Employment: 19600)
+6. **EV wiring harnesses and power distribution**:
+   - Woodbridge Foam Corp. (Employment: 1657)
+7. **EV and ICE component manufacturing**:
+   - Vista Metals Corp. (Employment: 1500)
+The top three roles by total employment are:
+1. **Advanced electrical architecture for EVs**: Yamaha Motor Manufacturing Corp., Employment: 190,000
+2. **OEM parent group footprint (EV + HD electrification)**: TN Americas Holding Inc., Employment: 196</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>5.91</v>
+        <v>5.89</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -3903,7 +3929,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="K57" t="b">
         <v>0</v>
@@ -3914,7 +3940,7 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="N57" t="b">
         <v>0</v>
@@ -3944,12 +3970,12 @@
       <c r="F58" t="inlineStr">
         <is>
           <t>For Tier 1 suppliers in Georgia's EV supply chain:
-- **Minimum Employment:** PPG Industries Inc. with 120 employees.
-- **Maximum Employment:** Linde + Wiemann with 515 employees.</t>
+- **Minimum Employment**: PPG Industries Inc. with 120 employees.
+- **Maximum Employment**: Linde + Wiemann with 515 employees.</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -3960,7 +3986,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="K58" t="b">
         <v>0</v>
@@ -3971,7 +3997,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="N58" t="b">
         <v>0</v>
@@ -3999,7 +4025,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>To calculate the average employment for Tier 2/3 suppliers within each Industry Group based on the provided context:
+          <t>To calculate the average employment for Tier 2/3 suppliers within each industry group based on the provided context:
 1. **Textile Products**:
    - Adient | Employment: 180
 2. **Rubber and Miscellaneous Plastic Products**:
@@ -4009,12 +4035,12 @@
 4. **Primary Metal Industries**:
    - Ecoplastic Corporation | Employment: 160
    - Dongwon Autopart Technology Georgia LLC | Employment: 315
-Average employment for Tier 2/3 suppliers by Industry Group:
+Average employment by Industry Group for Tier 2/3 suppliers:
 - Textile Products: 180 (only one company)
 - Rubber and Miscellaneous Plastic Products: 250 (only one company)
 - Machinery Except Electrical: 200 (only one company)
-- Primary Metal Industries: (160 + 315) / 2 = 237.5
-Thus, the average employment for Tier 2/3 suppliers by Industry Group is as follows:
+- Primary Metal Industries: (160 + 315) / 2 = 475 / 2 = 237.5
+Thus, the average employment by Industry Group for Tier 2/3 suppliers is:
 - Textile Products: 180
 - Rubber and Miscellaneous Plastic Products: 250
 - Machinery Except Electrical: 200
@@ -4022,7 +4048,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>5.52</v>
+        <v>5.64</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -4044,7 +4070,7 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="N59" t="b">
         <v>0</v>
@@ -4072,11 +4098,11 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>The county with the highest total employment among Tier 1 suppliers is Troup County. This is based on the data from Linde + Wiemann (515 employees) and PPG Industries Inc. (120 employees), totaling 635 employees in Troup County.</t>
+          <t>The county with the highest total employment among Tier 1 suppliers is Troup County. This is based on data from Linde + Wiemann (515 employees) and PPG Industries Inc. (120 employees), totaling 635 employees in Troup County.</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -4087,7 +4113,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="K60" t="b">
         <v>0</v>
@@ -4131,7 +4157,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -4142,7 +4168,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="K61" t="b">
         <v>0</v>
@@ -4182,11 +4208,11 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Based on the provided context, there are no companies listed with a Primary Facility Type of "R&amp;D". Therefore, it's not possible to identify any company meeting this criterion.</t>
+          <t>Based on the provided context, there are no companies listed with a Primary Facility Type of "R&amp;D". Therefore, it's not possible to identify any company meeting this criterion that has the highest employment.</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -4197,7 +4223,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="K62" t="b">
         <v>0</v>
@@ -4237,11 +4263,11 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Based on the provided context, there is no company listed with employment between 200 and 500 employees (inclusive) that has "EV / Battery Relevant" marked as Yes. The closest in terms of employee numbers are Hitachi Astemo Americas Inc., which employs 723 people, but it falls outside the specified range.</t>
+          <t>Based on the provided context, there are no companies listed with employment between 200 and 500 employees (inclusive) that are EV/Battery Relevant = Yes.</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>1.82</v>
+        <v>1.23</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -4263,7 +4289,7 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="N63" t="b">
         <v>0</v>
@@ -4291,11 +4317,11 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>The Industry Group with the highest total employment is **Electrical connectors and sensors**, with Woory Industrial Co. having 87,000 employees in Georgia.</t>
+          <t>The Industry Group with the highest total employment is **Electrical Connectors and Sensors**, which includes Woory Industrial Co. with 87,000 employees.</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -4306,7 +4332,7 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="K64" t="b">
         <v>0</v>
@@ -4346,16 +4372,28 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>To determine the category with the highest average employment based on the provided context:
-- **OEM (Footprint)** includes Toyota Industries Group (TACG-TICA) and Trenton Pressing. The average employment is \((18100 + 350) / 2 = 9225\).
-- **Tier 2/3** includes Adient, with an employment of 180.
-- **Tier 1** includes Linde + Wiemann, with an employment of 515.
-- **OEM Supply Chain** includes WIKA USA, Valeo, Volvo Cars USA, and Wabash National Corp. The average employment is \((250000 + 269 + 456 + 20) / 4 = 62731\).
-The category with the highest average employment is **OEM Supply Chain** at an average of 62,731 employees.</t>
+          <t>To determine the category with the highest average employment from the provided context:
+1. **OEM (Footprint)**:
+   - Companies: Toyota Industries Group (TACG-TICA), Trenton Pressing
+   - Employment Totals: 18,100 + 350 = 18,450
+   - Average Employment: \( \frac{18,450}{2} = 9,225 \)
+2. **Tier 2/3**:
+   - Companies: Adient
+   - Employment Totals: 180
+   - Average Employment: \( \frac{180}{1} = 180 \)
+3. **Tier 1**:
+   - Companies: Linde + Wiemann
+   - Employment Totals: 515
+   - Average Employment: \( \frac{515}{1} = 515 \)
+4. **OEM Supply Chain**:
+   - Companies: WIKA USA, Valeo, Volvo Cars USA, Wabash National Corp.
+   - Employment Totals: 250,000 + 269 + 456 + 20 = 251,145
+   - Average Employment: \( \frac{251,145}{4} = 62,786.25 \)
+The category</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>4.12</v>
+        <v>5.83</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -4366,7 +4404,7 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K65" t="b">
         <v>0</v>
@@ -4405,17 +4443,17 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>The companies in Georgia's EV supply chain with employment of 10,000 or more are:
+          <t>The companies in Georgia within the EV supply chain that have employment of 10,000 or more are:
 - **Toyota Industries Group (TACG-TICA)**
-  - Category: OEM (Footprint)
-  - Classification Method: Public OEM footprint / supplier listing
+  - **Category:** OEM (Footprint)
+  - **Classification Method:** Public OEM footprint / supplier listing
 - **Yazaki North America**
-  - Category: OEM Footprint
-  - Classification Method: Public OEM footprint / supplier listing</t>
+  - **Category:** OEM Footprint
+  - **Classification Method:** Public OEM footprint / supplier listing</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -4426,7 +4464,7 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="K66" t="b">
         <v>0</v>
@@ -4437,7 +4475,7 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="N66" t="b">
         <v>0</v>
@@ -4466,11 +4504,11 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Among the provided categories, the category **OEM (Footprint)** has the highest total employment. This is based on the data from TN Americas Holding Inc., which reports an employment of 19600 and Toyota Industries Group (TACG-TICA) with 18100 employees, both falling under the OEM (Footprint) category.</t>
+          <t>Among the provided categories, **OEM (Footprint)** has the highest total employment. This is based on data from TN Americas Holding Inc., which reports 19600 employees and Toyota Industries Group (TACG-TICA) with 18100 employees, both categorized under OEM (Footprint).</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -4481,7 +4519,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="K67" t="b">
         <v>0</v>
@@ -4521,11 +4559,11 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>The EV Supply Chain Role "General Automotive" is most concentrated in Troup County. This can be seen from multiple companies located there including PPG Industries Inc., Stryten Energy, Linde + Wiemann (mentioned twice but considered once), and PAI Industries Inc. All these companies have their primary facilities in Troup County and are categorized under the "General Automotive" role.</t>
+          <t>The EV Supply Chain Role of "General Automotive" is most concentrated in Troup County. This can be seen from multiple companies listed as having this role and located in Troup County: PPG Industries Inc., Stryten Energy, Linde + Wiemann (listed twice but relevant only once), and PAI Industries Inc.</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -4536,18 +4574,18 @@
         </is>
       </c>
       <c r="J68" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K68" t="b">
+        <v>0</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
         <v>0.1</v>
-      </c>
-      <c r="K68" t="b">
-        <v>0</v>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="M68" t="n">
-        <v>0.09</v>
       </c>
       <c r="N68" t="b">
         <v>0</v>
@@ -4581,7 +4619,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -4592,7 +4630,7 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="K69" t="b">
         <v>0</v>
@@ -4633,13 +4671,14 @@
       <c r="F70" t="inlineStr">
         <is>
           <t>Based on the provided context, the counties with the fewest companies are:
-1. Troup County: Contains entries for ADVICS Manufacturing Georgia LLC and Sejong Georgia LLC (2 companies).
-2. Coweta County: Contains an entry for Dongwon Autopart Technology Georgia LLC (1 company).
-Since only two counties are mentioned in the provided context, they cannot be ranked further to provide a bottom 5 list. However, Troup County has more entries than Coweta County specifically regarding these companies.</t>
+1. Troup County: Contains entries for ADVICS Manufacturing Georgia LLC and Sejong Georgia LLC (two instances), Joon Georgia, Inc. (two instances) - total of 4 unique company entries.
+2. Coweta County: Contains one entry each for Dongwon Autopart Technology Georgia LLC (two instances) - total of 1 unique company entry.
+Since the question asks for counties with the fewest companies and we only have two distinct county locations mentioned, Troup County has more companies than Coweta County. Therefore, the bottom 5 is not applicable as there are fewer than five unique counties listed. The single county with the fewest companies (excluding Georgia) is:
+Coweta County: Dongwon Autopart Technology Georgia LLC</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>2.28</v>
+        <v>3.44</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -4661,7 +4700,7 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="N70" t="b">
         <v>0</v>
@@ -4690,11 +4729,11 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>In Troup County, there is only one Tier 1 supplier named Stryten Energy. However, upon closer inspection of the provided sources, it appears there are multiple Tier 1 suppliers listed for Troup County (Linde + Wiemann, PPG Industries Inc., and Sejong Georgia LLC). Therefore, no single Tier 1 supplier exists uniquely in a county based on the given information.</t>
+          <t>In Troup County, there is only one Tier 1 supplier named Stryten Energy. However, it's important to note that Troup County has multiple Tier 1 suppliers including Linde + Wiemann and PPG Industries Inc., so the statement about having only one Tier 1 supplier does not hold true for Troup County based on the given context. No other county is mentioned as having a single Tier 1 supplier according to the provided information.</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -4705,7 +4744,7 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="K71" t="b">
         <v>0</v>
@@ -4745,14 +4784,14 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>The company that appears multiple times in the dataset is ZF Gainesville LLC. The distinct EV Supply Chain Roles recorded for this company are:
-1. EV thermal management and power electronics
-2. EV body, powertrain, and thermal components
-3. EV thermal systems and electronics</t>
+          <t>The company ZF Gainesville LLC appears multiple times in the dataset with distinct EV Supply Chain Roles:
+1. **EV thermal management and power electronics**
+2. **EV body, powertrain, and thermal components**
+3. **EV thermal systems and electronics**</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -4774,7 +4813,7 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="N72" t="b">
         <v>0</v>
@@ -4803,18 +4842,23 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>For ZF Gainesville LLC, the provided sources indicate variations in categories, EV supply chain roles, and locations as follows:
-1. **Category**: OEM Supply Chain (Sources 1, 2, 4, 5), OEM Footprint (Sources 3, 6)
-2. **EV Supply Chain Role**:
-   - EV thermal management and power electronics (Sources 1, 5)
-   - EV body, powertrain, and thermal components (Sources 2, 4)
-   - EV thermal systems and electronics (Sources 3, 6)
-3. **Location**: Georgia (All sources)
-These variations reflect different aspects of the company's operations within the electric vehicle supply chain in Georgia.</t>
+          <t>For ZF Gainesville LLC, comparing across different sources:
+- **Category**:
+  - Source 1 &amp; 3: OEM Footprint
+  - Sources 2, 4, 5, 6: OEM Supply Chain
+- **EV Supply Chain Role**:
+  - Source 1: EV thermal management and power electronics
+  - Source 2: EV body, powertrain, and thermal components
+  - Source 3: EV thermal systems and electronics
+  - Sources 4 &amp; 5: EV body, powertrain, and thermal components (Source 4) / EV thermal management and power electronics (Source 5)
+  - Source 6: EV thermal systems and electronics
+- **Location**:
+  - All sources list Georgia as the location.
+ZF Gainesville LLC is consistently identified across multiple sources with slight variations in its category classification, roles within the EV supply chain, but remains consistent in its geographical location in Georgia.</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>3.12</v>
+        <v>3.97</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -4825,7 +4869,7 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>0.19</v>
+        <v>0.09</v>
       </c>
       <c r="K73" t="b">
         <v>0</v>
@@ -4836,7 +4880,7 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="N73" t="b">
         <v>0</v>
@@ -4872,7 +4916,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -4883,7 +4927,7 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="K74" t="b">
         <v>0</v>
@@ -4923,17 +4967,17 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>For Sewon America Inc., the recorded products/services and their associated locations are:
-1. **Product/Service:** Fire truck bodies  
-   **Location:** Marietta, Cobb County
-2. **Product/Service:** Automotive aftermarket parts  
-   **Location:** Atlanta, Fulton County
-3. **Product/Service:** Motor vehicle engines and parts  
-   **Location:** Athens, Clarke County</t>
+          <t>For Sewon America Inc.:
+- **Product / Service:** Fire truck bodies  
+  - **Location:** Marietta, Cobb County
+- **Product / Service:** Automotive aftermarket parts  
+  - **Location:** Atlanta, Fulton County
+- **Product / Service:** Motor vehicle engines and parts  
+  - **Location:** Athens, Clarke County</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -4955,7 +4999,7 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="N75" t="b">
         <v>0</v>
@@ -4984,16 +5028,16 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>The Industry Group that has both Tier 1 and Tier 2/3 suppliers present is **Transportation Equipment**. 
-- **Tier 1 Supplier**: PPG Industries Inc.
-- **Tier 2/3 Suppliers**: Bosch (Automotive Division) falls under this category, although it's listed twice with similar information but no specific tier designation change in the provided context.
-Additionally, another Industry Group that fits is **Rubber and Miscellaneous Plastic Products**:
-- **Tier 2/3 Supplier**: Bosch (Automotive Division)
-However, based on the exact match of both tiers within a single group as per the given data, **Transportation Equipment** is the primary answer.</t>
+          <t>The Industry Group that has both Tier 1 and Tier 2/3 suppliers present is **Rubber and Miscellaneous Plastic Products**. 
+- **Tier 2/3 Supplier**: Bosch (Automotive Division) in Thomson, McDuffie County.
+- **Note**: Although there isn't a direct Tier 1 supplier listed under this category, the question asks for Industry Groups with both tiers present based on the provided context, and Bosch is the only company mentioned under "Rubber and Miscellaneous Plastic Products."
+Additionally, another relevant Industry Group is **Transportation Equipment**, which includes:
+- **Tier 1 Supplier**: PPG Industries Inc. in Troup County.
+However, no Tier 2/3 suppliers are listed for this group specifically based on the given context.</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>2.98</v>
+        <v>3.28</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -5015,7 +5059,7 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="N76" t="b">
         <v>0</v>
@@ -5044,11 +5088,11 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>The county with the highest number of Materials entries is Bulloch County. The company in this category is Ascend Elements, which provides interior and exterior plastic parts for the automotive industry.</t>
+          <t>The county with the highest number of Materials entries is Bulloch County. The company in this category is Ascend Elements.</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -5070,7 +5114,7 @@
         </is>
       </c>
       <c r="M77" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="N77" t="b">
         <v>0</v>
@@ -5099,15 +5143,15 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Battery Pack or Battery Cell activities are present in two counties:
+          <t>Battery Pack or Battery Cell activities are found in two counties:
 1. **Bryan County**: 
-   - 1 company (Honda Development &amp; Manufacturing) involved in Battery Cells for electric mobility with employment of 400 people.
+   - 1 company (Honda Development &amp; Manufacturing) involved in Battery Cells for electric mobility with 400 employees.
 2. **Coweta County**:
-   - 1 company (Hitachi Astemo Americas Inc.) involved in Battery Cells for electric mobility with employment of 723 people.</t>
+   - 1 company (Hitachi Astemo Americas Inc.) involved in Battery Cells for electric mobility with 723 employees.</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -5118,7 +5162,7 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K78" t="b">
         <v>0</v>
@@ -5159,13 +5203,20 @@
       <c r="F79" t="inlineStr">
         <is>
           <t>The companies marked as EV / Battery Relevant = No but still categorized as Tier 1 or Tier 1/2 are:
-- **FREYR Battery**: Product / Service: Decorative and functional coating systems.
-- **SK Battery America**: Product / Service: Engineered steel systems mounted in motor vehicles.
-- **Hyundai &amp; LG Energy Solution (LGES)**: Product / Service: Storage batteries.</t>
+- **FREYR Battery**
+  - Product / Service: Decorative and functional coating systems
+- **SK Battery America**
+  - Product / Service: Engineered steel systems mounted in motor vehicles
+- **Hyundai &amp; LG Energy Solution (LGES)**
+  - Product / Service: Storage batteries
+- **Stryten Energy**
+  - Product / Service: Automotive fiber padding
+- **PPG Industries Inc.**
+  - Product / Service: Muffler and exhaust systems</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>2.05</v>
+        <v>2.83</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -5176,7 +5227,7 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="K79" t="b">
         <v>0</v>
@@ -5216,24 +5267,18 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>In the provided dataset, there are two Supplier or Affiliation Type categories:
-1. **Automotive supply chain participant**: This category includes 6 companies:
-   - Adient
-   - Haering Precision USA LP
-   - Robert Bosch LLC
-   - Trenton Pressing (Note: Although Trenton Pressing's primary role is OEM corporate footprint and supplier integration, it also participates in the automotive supply chain.)
-   - Vista Metals Corp.
-   - Vanguard National Trailer Corp.
-2. **OEM**: This category includes 2 companies:
-   - Toyota Industries Group (TACG-TICA) appears twice but represents a single entity with different roles described.
-   - Trenton Pressing is also listed under OEM corporate footprint, indicating its role as an OEM in addition to being part of the supply chain.
-However, if we are strictly categorizing based on the "Supplier or Affiliation Type" field and excluding repeated entries or secondary classifications:
-- **Automotive supply chain participant**: 6 companies
-- **OEM**: 1 company (Toyota Industries Group)</t>
+          <t>The Supplier or Affiliation Type categories existing in the dataset are "Automotive supply chain participant" and no other types. There are six companies falling under this category:
+1. Adient
+2. Haering Precision USA LP
+3. Robert Bosch LLC
+4. Toyota Industries Group (TACG-TICA) - although it also falls under OEM, its supplier listing is considered here.
+5. Trenton Pressing
+6. Vista Metals Corp.
+Note: While Toyota Industries Group appears twice in the dataset, one instance is specifically noted for its EV supply chain role and footprint, which aligns with the "Automotive supply chain participant" type when considering its supplier listing aspect. However, it primarily operates as an OEM (Original Equipment Manufacturer).</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>4.4</v>
+        <v>3.26</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -5244,18 +5289,18 @@
         </is>
       </c>
       <c r="J80" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K80" t="b">
+        <v>0</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
         <v>0.11</v>
-      </c>
-      <c r="K80" t="b">
-        <v>0</v>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>Error: 403 Your API key was reported as leaked. Please use another API key.</t>
-        </is>
-      </c>
-      <c r="M80" t="n">
-        <v>0.09</v>
       </c>
       <c r="N80" t="b">
         <v>0</v>
@@ -5284,18 +5329,18 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Among the entries provided for Georgia EV supply chain companies, the following EV Supply Chain Roles are represented by companies affiliated with Original Equipment Manufacturers (OEMs):
+          <t>Among the provided entries for Georgia EV supply chain companies with a focus on those involved in the original equipment manufacturer (OEM) supply chain, the following EV Supply Chain Roles are represented:
 1. **EV body, powertrain, and thermal components** - ZF Gainesville LLC
 2. **Body and chassis components for EV and ICE OEMs** - Vanguard National Trailer Corp.
 3. **EV wiring harnesses and power distribution** - Woodbridge Foam Corp.
 4. **Advanced electrical architecture for EVs** - Yamaha Motor Manufacturing Corp.
 5. **EV thermal management and power electronics** - ZF Gainesville LLC
 6. **High-voltage EV connectors and electronics** - Woory Industrial Co.
-These roles are cited based on the companies' specific contributions to the electric vehicle supply chain as detailed in the provided context.</t>
+These roles cover critical components of the electric vehicle supply chain, including structural elements, electrical systems, and thermal management solutions.</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>3.41</v>
+        <v>3.51</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -5306,7 +5351,7 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>0.21</v>
+        <v>0.09</v>
       </c>
       <c r="K81" t="b">
         <v>0</v>
@@ -5317,7 +5362,7 @@
         </is>
       </c>
       <c r="M81" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="N81" t="b">
         <v>0</v>
@@ -5346,17 +5391,17 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Based on the provided context, none of the listed Georgia EV supply chain companies are noted as having missing Primary OEMs. However, the question seems to imply identifying companies without explicitly named primary Original Equipment Manufacturers (OEMs), which would mean focusing on their roles directly:
-- **Vanguard National Trailer Corp.** has an EV Supply Chain Role of body and chassis components for both EV and ICE OEMs.
-- **Woory Industrial Co.** provides high-voltage EV connectors and electronics.
-- **ZF Gainesville LLC** (listed twice but with different focus areas) is involved in EV body, powertrain, and thermal components as well as EV thermal management and power electronics.
-- **Vista Metals Corp.** manufactures EV and ICE component parts.
-- **Yamaha Motor Manufacturing Corp.** focuses on advanced electrical architecture for EVs.
-These companies are directly engaged in the EV supply chain without a specific primary OEM listed, meaning they serve multiple or unspecified OEMs within their roles.</t>
+          <t>Based on the provided context, there are no companies listed that have missing Primary OEMs. However, if you're asking about their EV Supply Chain Roles:
+1. **ZF Gainesville LLC**: Has multiple roles including EV body, powertrain, and thermal components; and EV thermal management and power electronics.
+2. **Vanguard National Trailer Corp.**: Body and chassis components for EV and ICE OEMs.
+3. **Woory Industrial Co.**: High-voltage EV connectors and electronics.
+4. **Vista Metals Corp.**: EV and ICE component manufacturing.
+5. **Yamaha Motor Manufacturing Corp.**: Advanced electrical architecture for EVs.
+These companies are all part of the EV supply chain in Georgia, contributing to various aspects such as body components, thermal management, powertrain parts, connectors, and electronics.</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>3.97</v>
+        <v>3.39</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -5407,11 +5452,11 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>None of the provided context mentions any company with "Product / Service" text that includes the word "lithium." Therefore, there are no companies listed in the given information that meet this criterion.</t>
+          <t>None of the provided companies in the context mention "lithium" in their product or service descriptions. Therefore, there are no companies that fit the criteria specified in the question.</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -5462,11 +5507,11 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>None of the provided companies in the context are described as recyclers in their Product/Service details. All listed companies deal with manufacturing or supply chain roles related to automotive components, metal stamping, textiles for interiors, and commercial vehicle operations. There is no mention of recycling activities among these firms. Therefore, there are no relevant companies fitting the criteria specified in the question.</t>
+          <t>None of the provided companies in the context are described as recyclers in their product or service offerings. All listed companies provide services related to manufacturing components for the automotive industry, such as metal stamping, fabrication, and textile components, but none mention recycling specifically. The categories associated with these companies include OEM Supply Chain and OEM (Footprint).</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -5477,7 +5522,7 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K84" t="b">
         <v>0</v>
@@ -5519,16 +5564,14 @@
         <is>
           <t>The companies that provide wiring harness-related products/services in Georgia are:
 1. **Woodbridge Foam Corp.**
-   - EV Supply Chain Role: EV wiring harnesses and power distribution
-   - Product / Service: Automotive wiring harnesses &amp; electrical distribution systems
+   - Product/Service: Automotive wiring harnesses &amp; electrical distribution systems
 2. **WIKA USA**
-   - EV Supply Chain Role: HV and LV wiring harnesses for EVs and ICE vehicles
-   - Product / Service: Vehicle power &amp; data solutions; wiring harnesses and connectors
-Neither of these companies specifically mentions primary OEMs in the provided context.</t>
+   - Product/Service: Vehicle power &amp; data solutions; wiring harnesses and connectors
+Neither of these companies specifies their primary OEMs (Original Equipment Manufacturers) in the provided context.</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>2.51</v>
+        <v>1.97</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -5579,11 +5622,11 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>The companies that mention 'connectors' in their Product / Service description are Woory Industrial Co. Both instances of Woory Industrial Co. list connectors as part of their product/service offerings and have an EV / Battery Relevant status of "Yes".</t>
+          <t>The companies that mention 'connectors' in their Product / Service are Woory Industrial Co. Both instances of Woory Industrial Co. list connectors as part of their product/service offerings and have an "EV / Battery Relevant" status marked as "Yes".</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -5594,7 +5637,7 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="K86" t="b">
         <v>0</v>
@@ -5605,7 +5648,7 @@
         </is>
       </c>
       <c r="M86" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="N86" t="b">
         <v>0</v>
@@ -5636,13 +5679,15 @@
         <is>
           <t>The companies whose Product / Service mentions 'thermal' are:
 1. **ZF Gainesville LLC**
-   - **EV Supply Chain Role:** EV thermal management and power electronics | EV thermal systems and electronics
-   - **Primary Facility Type:** Manufacturing | Engineering / Operations
-No other company in the provided context mentions 'thermal' in their product or service description.</t>
+   - **EV Supply Chain Role:** EV thermal management and power electronics
+   - **Primary Facility Type:** Manufacturing
+2. **ZF Gainesville LLC** (another instance)
+   - **EV Supply Chain Role:** EV thermal systems and electronics
+   - **Primary Facility Type:** Engineering / Operations</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -5653,7 +5698,7 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="K87" t="b">
         <v>0</v>
@@ -5664,7 +5709,7 @@
         </is>
       </c>
       <c r="M87" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="N87" t="b">
         <v>0</v>
@@ -5711,7 +5756,7 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="K88" t="b">
         <v>0</v>
@@ -5722,7 +5767,7 @@
         </is>
       </c>
       <c r="M88" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="N88" t="b">
         <v>0</v>
@@ -5751,7 +5796,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>The company that mentions "sensors" in its Product/Service description is Woory Industrial Co. Its EV Supply Chain Role is "High-voltage EV connectors and electronics."</t>
+          <t>The company that mentions 'sensors' in its Product/Service description is Woory Industrial Co. Its EV Supply Chain Role is "High-voltage EV connectors and electronics."</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -5766,7 +5811,7 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="K89" t="b">
         <v>0</v>
@@ -5807,22 +5852,23 @@
       <c r="F90" t="inlineStr">
         <is>
           <t>**Classification Method: Public OEM footprint / supplier listing**
-- **Number of Companies:** 4
-- **Top 5 by Employment:**
-  1. Toyota Industries Group (TACG-TICA) - 18,100 employees
-  2. Vista Metals Corp. - 1,500 employees
-  3. Trenton Pressing - 350 employees
+- Number of Companies: 4 (Toyota Industries Group [TACG-TICA], Valeo, Trenton Pressing, Vista Metals Corp.)
+- Top 5 by Employment:
+  1. Toyota Industries Group (TACG-TICA) - 18100
+  2. Vista Metals Corp. - 1500
+  3. Trenton Pressing - 350
+  4. Valeo - 269
 **Classification Method: Supplier**
-- **Number of Companies:** 4
-- **Top 5 by Employment:**
-  1. Linde + Wiemann - 515 employees
-  2. NIFCO KTW America Corp. - 300 employees
-  3. Adient - 180 employees
-  4. Haering Precision USA LP - 200 employees</t>
+- Number of Companies: 4 (Adient, NIFCO KTW America Corp., Linde + Wiemann, Haering Precision USA LP)
+- Top 5 by Employment:
+  1. Adient - 180
+  2. NIFCO KTW America Corp. - 300
+  3. Linde + Wiemann - 515
+  4. Haering Precision USA LP - 200</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>3.64</v>
+        <v>4.4</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -5833,7 +5879,7 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="K90" t="b">
         <v>0</v>
@@ -5873,34 +5919,32 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Entries classified as 'Public OEM footprint / supplier listing' include the following companies with their respective categories and EV/Battery Relevant statuses:
+          <t>The entries classified as 'Public OEM footprint / supplier listing' with their respective categories and EV/Battery Relevant statuses are:
 1. **TN Americas Holding Inc.**
    - Category: OEM (Footprint)
-   - EV/Battery Relevant: Yes
-2. **ZF Gainesville LLC** (two entries, but both relevant to EV supply chain)
+   - EV / Battery Relevant: Yes
+2. **ZF Gainesville LLC** (two instances, but listed once for clarity)
    - Category: OEM Footprint
-   - EV/Battery Relevant: Yes
-   - Category: OEM Supply Chain
-   - EV/Battery Relevant: Yes
+   - EV / Battery Relevant: Yes
 3. **Yazaki North America**
    - Category: OEM Footprint
-   - EV/Battery Relevant: Yes
+   - EV / Battery Relevant: Yes
 4. **Valeo**
    - Category: OEM Supply Chain
-   - EV/Battery Relevant: Yes
+   - EV / Battery Relevant: Yes
 5. **Vista Metals Corp.**
    - Category: OEM Supply Chain
-   - EV/Battery Relevant: Yes
+   - EV / Battery Relevant: Yes
 6. **Yamaha Motor Manufacturing Corp.**
    - Category: OEM Supply Chain
-   - EV/Battery Relevant: Yes
+   - EV / Battery Relevant: Yes
 7. **Woodbridge Foam Corp.**
    - Category: OEM Supply Chain
-   - EV/Battery Relevant: Yes</t>
+   - EV / Battery Relevant: Yes</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>4.72</v>
+        <v>4.38</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -5958,13 +6002,13 @@
    - **EV Supply Chain Role:** EV wiring harnesses and power distribution
 3. **ZF Gainesville LLC**
    - **EV Supply Chain Role:** EV thermal management and power electronics
-   - Additionally, ZF Gainesville LLC also covers EV body, powertrain, and thermal components.
+   - Additionally, ZF Gainesville LLC is involved in EV body, powertrain, and thermal components.
 4. **Yamaha Motor Manufacturing Corp.**
    - **EV Supply Chain Role:** Advanced electrical architecture for EVs</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -5975,7 +6019,7 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K92" t="b">
         <v>0</v>
@@ -5986,7 +6030,7 @@
         </is>
       </c>
       <c r="M92" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="N92" t="b">
         <v>0</v>
@@ -6030,7 +6074,7 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="K93" t="b">
         <v>0</v>
@@ -6070,18 +6114,17 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>The companies that have a Category indicating an OEM-related classification but do not fill in the Supplier or Affiliation Type are:
+          <t>The companies where the Category indicates an OEM-related class but the Supplier or Affiliation Type is not filled are:
 1. Vista Metals Corp.
 2. Valeo
 3. TN Americas Holding Inc.
 4. Yamaha Motor Manufacturing Corp.
 5. Toyota Industries Group (TACG-TICA)
-6. Vernay
-These companies all have a Category starting with 'OEM' and do not specify a Supplier or Affiliation Type in the provided context.</t>
+6. Vernay</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>2.27</v>
+        <v>1.73</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -6092,7 +6135,7 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K94" t="b">
         <v>0</v>
@@ -6132,11 +6175,11 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>The provided context does not specify an exact minimum employment threshold for including companies in the dataset. However, it lists several companies with varying numbers of employees, indicating that there isn't a uniform low number set as a strict threshold since even small-scale operations like Wabash National Corp. (20 employees) are included alongside larger entities such as Toyota Industries Group (18100 employees). Therefore, based on the given information, no specific minimum employment threshold can be cited directly from the provided data.</t>
+          <t>The provided context does not specify an exact minimum employment threshold for including companies in the dataset. However, it lists several companies with varying numbers of employees, indicating that there isn't a uniform cutoff based on employment alone. For example, Adient employs 180 people while Toyota Industries Group (TACG-TICA) has 18,100 employees. Therefore, no single minimum threshold can be cited from the given information.</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
@@ -6158,7 +6201,7 @@
         </is>
       </c>
       <c r="M95" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="N95" t="b">
         <v>0</v>
@@ -6187,16 +6230,16 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>According to the provided context, the Location field includes both city and county information. For example:
-- **Trenton Pressing**: Located in Georgia (no specific city mentioned).
-- **Linde + Wiemann**: Located in Troup County.
+          <t>According to the provided context, the Location field for Georgia EV supply chain companies includes both city and county information. For example:
+- **Trenton Pressing**: Location listed as "Georgia" (no specific city or county mentioned).
+- **Linde + Wiemann**: Listed in Troup County.
 - **First American Resources**: Located in Albany, Dougherty County.
 - **TI Fluid Systems**: Located in Atlanta, Fulton County.
-The City values are standardized by including the county name when applicable. For instance, "Atlanta, Fulton County" provides both city and county information clearly.</t>
+The City values are standardized by including the city name followed by the county name when applicable.</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -6218,7 +6261,7 @@
         </is>
       </c>
       <c r="M96" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="N96" t="b">
         <v>0</v>
@@ -6247,16 +6290,16 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>The context provided mentions several roles within the EV supply chain. The roles explicitly listed are:
+          <t>The context provided mentions several EV Supply Chain Roles. The roles explicitly listed are:
 1. **EV thermal management and power electronics**
 2. **EV wiring harnesses and power distribution**
 3. **EV body, powertrain, and thermal components**
 4. **High-voltage EV connectors and electronics**
-These roles are associated with companies such as ZF Gainesville LLC, Woodbridge Foam Corp., Woory Industrial Co., and TI Fluid Systems in the context of Georgia's EV supply chain.</t>
+These roles are associated with companies such as ZF Gainesville LLC, Woodbridge Foam Corp., Woory Industrial Co., and TI Fluid Systems in the context of their operations in Georgia related to electric vehicle supply chains.</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -6267,7 +6310,7 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="K97" t="b">
         <v>0</v>
@@ -6278,7 +6321,7 @@
         </is>
       </c>
       <c r="M97" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="N97" t="b">
         <v>0</v>
@@ -6320,7 +6363,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -6331,7 +6374,7 @@
         </is>
       </c>
       <c r="J98" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="K98" t="b">
         <v>0</v>
@@ -6342,7 +6385,7 @@
         </is>
       </c>
       <c r="M98" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="N98" t="b">
         <v>0</v>
@@ -6372,13 +6415,13 @@
       <c r="F99" t="inlineStr">
         <is>
           <t>The company with Primary Facility Type = Regional corporate operations is:
-- **Trenton Pressing**
-  - **Category:** OEM (Footprint)
-  - **Location:** Georgia</t>
+- **Trenton Pressing**:
+  - Category: OEM (Footprint)
+  - Location: Georgia</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -6389,7 +6432,7 @@
         </is>
       </c>
       <c r="J99" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="K99" t="b">
         <v>0</v>
@@ -6439,7 +6482,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -6490,11 +6533,11 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Within Tier 1 suppliers, the company in the category of 'Electronic and Other Electrical Equipment and Components' is Woory Industrial Co. Their product/service includes automotive connectors, terminals, sensors, and power/data components.</t>
+          <t>Within the Tier 1 suppliers listed, Woory Industrial Co. falls under the category of 'Electronic and Other Electrical Equipment and Components'. The product/service provided by Woory Industrial Co. is automotive connectors, terminals, sensors, and power/data components.</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -6545,14 +6588,11 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>According to the provided context, supply chain tiers are assigned based on the company's role in the automotive industry. Specifically:
-- **Tier 1**: Companies that directly supply components or systems to Original Equipment Manufacturers (OEMs). For example, Linde + Wiemann and Robert Bosch LLC are categorized as Tier 1 suppliers providing general automotive parts like transmissions and powertrain systems.
-- **Tier 2/3**: Companies that supply tools, dies, or materials used in the production of components for OEMs. Haering Precision USA LP is an example of a Tier 2/3 supplier that provides tools and dies for the automotive industry.
-The classification method described involves identifying whether companies are direct suppliers to OEMs (Tier 1) or provide indirect support through manufacturing aids and materials (Tier 2/3).</t>
+          <t>According to the provided context, supply chain tiers are assigned based on the company's role in the automotive industry. Companies like Valeo and Robert Bosch LLC are categorized as Tier 1 suppliers because they provide direct components or systems to OEMs (Original Equipment Manufacturers). For example, Valeo is listed under "Category: OEM Supply Chain" with an EV Supply Chain Role of "Tier 1 automotive components," indicating it supplies directly to the automakers. Haering Precision USA LP and Bosch (Automotive Division) are categorized as Tier 2/3 suppliers because they provide tools or materials used in manufacturing processes for automotive parts, which is less direct than Tier 1's interaction with OEMs.</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>3.43</v>
+        <v>2.98</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -6563,7 +6603,7 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K102" t="b">
         <v>0</v>
@@ -6574,7 +6614,7 @@
         </is>
       </c>
       <c r="M102" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="N102" t="b">
         <v>0</v>
